--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45441</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44509</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45796</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45993</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>46078</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45155</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>45845</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45028</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44762</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>46171</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>46171</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>46064</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>46182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>45545</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>46090</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>46133</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45384</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>46227</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46268</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45786</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>46261</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>46240</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45842</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45842</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45772</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45335</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46013</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44465</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44510</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45335</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45489</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45678</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45152</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45335</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45069</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45356</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45608</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44664</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45037</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45419</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45232</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45258</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45653</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45147</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44834</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>45051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45435</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44887</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45162</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45250</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45644</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45659</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44649</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45414</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44770</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>45162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>45196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44924</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45443</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45385</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45261</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45547</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45475</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45562</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45562</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45562</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44566</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45250</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44817</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45224</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45433</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45005</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45673</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44790</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45090</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45106</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44776</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44904</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44628</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45629</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45033</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45201</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45201</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45244</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45310</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45581</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45103</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45625</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45733</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45840</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45716</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45469</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44757</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45264</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45323</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45484</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46136</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45786</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44687</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45838</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45148</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45796</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45450</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45390</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45783</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45149</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45145</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45891</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45839</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45166</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45510</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45401</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45425</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45873</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45645</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45469</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45739</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45729</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45699</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45898</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45898</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45772</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45846</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45902</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45902</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45905</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45905</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45847</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45905</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44526</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45097</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45266</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45769</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45684</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44638</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46141</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45909</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45824</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>46140</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>46141</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44824</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46141</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44915</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>46140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45833</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45790</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>46141</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>46141</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45201</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45918</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45684</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>44540</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45922</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45922</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45922</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46058</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45720</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>45925</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>46140</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45926</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45121</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46141</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45927</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45927</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>46142</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45684</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45509</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46142</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>46142</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45933</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>44937</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45087</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45932</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45933</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45933</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45933</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45527</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45933</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45937</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>46146</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45938</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45941</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>46149</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45371</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45713</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45947</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45947</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>44876</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45946</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45084</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44502</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45951</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>46150</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45949</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>46150</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45562</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45036</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45954</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45618</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44613</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45954</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45954</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45645</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46150</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>45960</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>45461</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45960</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45351</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45152</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>46155</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46155</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46155</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>45966</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45435</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45148</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45967</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45971</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>46155</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45968</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45975</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45975</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45057</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45975</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45429</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45975</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45979</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44763</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45226</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45476</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>45980</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45420</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>46155</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46155</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45720</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45338</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44984</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45525</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46160</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>46029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45533</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45287</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>46161</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45614</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45226</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>46160</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45765</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45502</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>46163</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45223</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45947</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45624</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45869</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45741</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45475</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45475</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45534</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45534</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>44582</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45996</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45999</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45996</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>46162</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45434</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45725</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45400</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45582</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46003</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46164</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>46002</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44567</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45526</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>46003</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>46003</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46007</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46006</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46164</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>46006</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>46006</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>46006</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45831</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45831</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45140</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45741</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>46008</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44883</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45328</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>46010</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>46010</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45575</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>46010</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45155</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44809</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45268</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45057</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46020</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45615</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>46020</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46018</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46018</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45470</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>46020</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>45562</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>45079</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45937</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>46029</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46171</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45441</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>46030</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>46030</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>46174</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>46034</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46171</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46171</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45212</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>46171</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45203</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45506</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>46171</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>46171</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>44951</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45282</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45684</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45436</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44949</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45575</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46171</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46048</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>44760</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46171</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>46048</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>46049</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45050</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46050</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46050</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46050</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46050</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>46050</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>46050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46177</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>46052</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46178</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44817</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>45681</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45400</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>46057</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45373</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45525</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46177</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46065</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46182</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>46181</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>46181</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>45110</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44903</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46072</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46182</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>44700</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46072</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46182</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46076</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45420</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45632</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45679</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46184</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>46184</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45398</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>46184</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46188</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46185</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46090</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>46188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46087</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>46188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45244</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>44596</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>46185</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>46185</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>46091</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>46189</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46094</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>46094</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46094</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>44465</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>46094</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>46094</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45054</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>46098</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>46189</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>46098</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45212</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>46098</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>46099</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>46191</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>46099</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45645</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45244</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>46104</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>46101</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>44610</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>46104</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>46101</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>46106</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46106</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>46106</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>46106</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>46106</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>46105</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46106</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>46106</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>46108</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>46198</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>44950</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>44950</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>46198</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>46198</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>46198</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>46108</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>46111</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46200</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>46200</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45518</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44830</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45428</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46524,7 +46524,7 @@
         <v>46106</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>46122</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>46122</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>46122</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45371</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45763</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>46126</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>46129</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>46127</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>46129</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>46245</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>45201</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>46204</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>46133</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>46133</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45259</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45532</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47893,7 +47893,7 @@
         <v>46133</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>46133</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>46132</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>46133</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>46134</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45211</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>44896</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45559</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>46134</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>46133</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>46203</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>46203</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>46139</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>46203</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46020</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45632</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>44694</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46203</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>46203</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45447</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45324</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>44571</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45446</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>45379</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49788,7 +49788,7 @@
         <v>45713</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>46251</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>46248</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>46206</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>46205</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>46248</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>46206</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45758</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45703</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>45414</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46251</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45684</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45226</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>46206</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>46248</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>45671</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>46209</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>46209</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45590</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>44883</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>45107</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>46252</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45609</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>45692</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45366</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51678,7 +51678,7 @@
         <v>44595</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>46209</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>46255</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>46254</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45258</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52053,7 +52053,7 @@
         <v>45258</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45328</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>46255</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45029</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45175</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>46254</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46255</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>46211</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>46254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52745,7 +52745,7 @@
         <v>45726</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45244</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52896,7 +52896,7 @@
         <v>45673</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>46213</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45562</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45172</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45201</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45492</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45519</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>44622</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46258</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46260</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>46260</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>44851</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45510</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>46261</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45618</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46261</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>44817</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46260</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45308</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45629</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45132</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45723</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>45572</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45386</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>46265</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45190</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>45562</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
         <v>45562</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>45562</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45562</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>44603</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>46265</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>46262</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45149</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>46267</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45264</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45264</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45764</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55760,7 +55760,7 @@
         <v>46269</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>46268</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>46268</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>46269</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>45035</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56150,7 +56150,7 @@
         <v>44770</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>45638</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>46226</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>46225</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45777</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>46225</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>46269</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>46272</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45783</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>46272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45460</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>44683</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>46268</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>46269</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
         <v>46269</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>46275</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>46274</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>46274</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>45587</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>46275</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>46274</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>46267</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>46275</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45169</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>46233</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>46233</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>46279</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45789</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58430,7 +58430,7 @@
         <v>46279</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58508,7 +58508,7 @@
         <v>45786</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58581,7 +58581,7 @@
         <v>46280</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58659,7 +58659,7 @@
         <v>46280</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>46280</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45791</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45790</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>46280</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>46280</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45545</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>46280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45790</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>46281</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>45623</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>45792</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59668,7 +59668,7 @@
         <v>45792</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59741,7 +59741,7 @@
         <v>45793</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59814,7 +59814,7 @@
         <v>45793</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>46282</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59965,7 +59965,7 @@
         <v>45615</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>46283</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60116,7 +60116,7 @@
         <v>45754</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60194,7 +60194,7 @@
         <v>46241</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60345,7 +60345,7 @@
         <v>46283</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60423,7 +60423,7 @@
         <v>46239</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60501,7 +60501,7 @@
         <v>46282</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>46239</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>46239</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60735,7 +60735,7 @@
         <v>45404</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>46283</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>45797</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>45797</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45797</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45736</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>46241</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>46241</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61339,7 +61339,7 @@
         <v>45799</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45799</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>45799</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>46239</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>46282</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>46282</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61797,7 +61797,7 @@
         <v>46282</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
         <v>45842</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>45807</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45754</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62104,7 +62104,7 @@
         <v>45546</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62177,7 +62177,7 @@
         <v>45811</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62250,7 +62250,7 @@
         <v>45608</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62323,7 +62323,7 @@
         <v>45810</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>45811</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45811</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62547,7 +62547,7 @@
         <v>45812</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>45812</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
         <v>45812</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>45811</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>45812</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45812</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>45211</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45819</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63161,7 +63161,7 @@
         <v>45818</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63239,7 +63239,7 @@
         <v>45821</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>45821</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63390,7 +63390,7 @@
         <v>45826</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>45826</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>45826</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45831</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>45841</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>45841</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45841</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45845</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>45845</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64077,7 +64077,7 @@
         <v>45845</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>45770</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64223,7 +64223,7 @@
         <v>45565</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>45784</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64369,7 +64369,7 @@
         <v>45854</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45854</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64525,7 +64525,7 @@
         <v>45793</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         <v>45838</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64671,7 +64671,7 @@
         <v>45824</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45874</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45569</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45356</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45750</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65046,7 +65046,7 @@
         <v>45812</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>44127</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65202,7 +65202,7 @@
         <v>44671</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45266</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>45266</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44606</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65514,7 +65514,7 @@
         <v>45266</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65592,7 +65592,7 @@
         <v>44834</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65670,7 +65670,7 @@
         <v>44606</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>45266</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65826,7 +65826,7 @@
         <v>44578</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65904,7 +65904,7 @@
         <v>44901</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45266</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66060,7 +66060,7 @@
         <v>44901</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45266</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45266</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>44606</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>45356</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>44606</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66523,7 +66523,7 @@
         <v>45247</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66601,7 +66601,7 @@
         <v>44901</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         <v>45316</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66752,7 +66752,7 @@
         <v>44901</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66830,7 +66830,7 @@
         <v>45680</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66908,7 +66908,7 @@
         <v>44606</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66986,7 +66986,7 @@
         <v>45247</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>45266</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67142,7 +67142,7 @@
         <v>44606</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67220,7 +67220,7 @@
         <v>44606</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67298,7 +67298,7 @@
         <v>45266</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67376,7 +67376,7 @@
         <v>45247</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>45247</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67532,7 +67532,7 @@
         <v>44901</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67610,7 +67610,7 @@
         <v>44901</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67766,7 +67766,7 @@
         <v>45266</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67844,7 +67844,7 @@
         <v>44901</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67922,7 +67922,7 @@
         <v>45716</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68000,7 +68000,7 @@
         <v>46037</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>46036</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>46013</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68234,7 +68234,7 @@
         <v>45691</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45993</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44532</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45384</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44889</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45799</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>45155</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46064</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>46133</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45028</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45845</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>45842</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46171</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45772</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46203</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44762</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>46265</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>46268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46227</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46261</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45062</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45786</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45335</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46013</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44465</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44510</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45713</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45621</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45681</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45268</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45414</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45414</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45373</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45338</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45400</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44770</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45401</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45441</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45434</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45425</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45244</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45398</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45562</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45443</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44812</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45420</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45366</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44834</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45226</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45371</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45533</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45258</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44984</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45435</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45435</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>46020</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46018</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46018</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>46020</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45140</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45793</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45404</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>46030</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45793</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45754</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44903</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45797</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46030</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44540</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45799</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45799</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45895</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45739</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45898</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45148</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46048</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45902</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45475</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45902</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>46050</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>46049</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46050</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46050</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46050</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45050</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45905</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45905</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45905</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46052</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45909</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46057</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44938</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45212</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45562</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45562</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45562</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45918</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45492</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45922</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45922</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45922</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45103</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45842</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>46072</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45033</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>44883</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45420</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45201</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45201</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45201</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45926</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45927</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>45930</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45379</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45927</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45928</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45932</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45546</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45807</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45608</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45754</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45933</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>46087</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45446</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45933</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45933</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45282</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45037</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45933</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45933</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46091</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45938</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46090</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>46094</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45941</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>46098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45946</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46099</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46098</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46101</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>46101</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45811</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46104</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45765</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45713</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45947</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45811</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>46105</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>46104</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45951</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>46106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46106</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>46106</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45562</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>46106</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45954</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>46106</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>46111</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>46108</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45954</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45812</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>46108</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45811</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45671</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45960</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45623</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45960</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46122</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>46122</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45132</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>46122</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46126</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45812</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45967</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45006</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45051</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45461</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45211</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>46127</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>46128</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45975</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46129</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>46129</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45980</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45436</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45980</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>46133</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>46134</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>46133</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46133</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46134</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45758</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46133</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45988</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45615</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45819</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>44757</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44694</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45152</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44770</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45818</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45838</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45684</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45996</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44896</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45097</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45999</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45201</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45833</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44817</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45057</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45783</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46136</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45786</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46003</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>46003</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46003</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45450</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46006</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46003</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45720</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46006</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>46007</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>46008</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46020</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45223</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45638</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45484</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45819</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46010</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>46010</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46139</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45328</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45791</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45873</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44937</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45821</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46140</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46140</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45796</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45155</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46140</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44809</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45469</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45469</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44851</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45826</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45826</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45525</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45733</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45846</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44790</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>46141</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46141</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44915</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44526</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46141</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>46141</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45461</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45769</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45826</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>46058</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45264</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44537</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46142</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>46142</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45054</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44571</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45758</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46146</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44924</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45831</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45261</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45741</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>44896</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44817</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45090</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44839</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>46150</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>46150</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46149</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46150</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45351</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44883</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46155</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46155</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45772</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>46155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45429</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45103</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>46160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46160</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45447</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45562</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45684</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46161</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45841</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45190</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45841</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46029</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>44950</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>44950</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>46162</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>46163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>46164</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45845</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45845</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45502</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46164</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45784</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45770</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45947</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45869</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45565</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45831</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44901</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45831</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45854</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45854</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45079</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46168</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46168</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45793</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>46171</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45519</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>46171</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45489</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>46171</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>46171</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46171</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45162</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46171</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46171</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45084</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>44951</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>46174</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45838</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46177</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46177</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44938</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45343</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46176</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>46177</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45475</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45475</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45428</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45335</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45035</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44567</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46181</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44622</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46178</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45720</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46181</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>46182</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46182</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46182</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>46182</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45107</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46185</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46185</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46185</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46185</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46184</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46184</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>46188</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>46188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>46189</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45547</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45145</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45526</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45629</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>46191</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45824</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45874</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>46195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44824</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45608</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45582</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45572</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45638</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45356</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45569</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44603</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>44596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46198</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45211</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45750</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45559</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45618</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>46198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45069</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46198</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45644</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45506</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46200</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46200</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46203</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>46203</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45645</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44664</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>46203</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46203</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>46203</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45659</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45812</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46251</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>46206</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45055</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49317,7 +49317,7 @@
         <v>46209</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45763</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>46206</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>46252</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45232</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45121</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45716</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45226</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45385</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46206</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>44613</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>46205</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45679</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>46251</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>46209</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>46211</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45692</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44638</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46254</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45149</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>45703</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46258</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45148</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>45107</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>44687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>46255</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>46213</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>46255</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>46254</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46254</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45244</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45684</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46260</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>46260</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45172</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45224</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46262</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46261</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45715</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45764</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46261</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45110</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>45645</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45279</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>46265</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45741</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>46265</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>46267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>46268</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>46225</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45250</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45723</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>45725</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>46272</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>46269</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>46269</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>46269</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
         <v>46268</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>44763</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>46272</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>46226</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45310</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46269</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46274</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>46274</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>46274</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>46267</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45211</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>45264</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>44595</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>46233</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>46275</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>44760</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>46275</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>46280</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55840,7 +55840,7 @@
         <v>45212</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>46280</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>46280</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>46280</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>44776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>46280</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>46279</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46233</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46280</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>46279</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56615,7 +56615,7 @@
         <v>46280</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45625</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45673</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46282</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>46282</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45476</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         <v>46239</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>46239</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>46282</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46281</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45534</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46282</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46282</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45509</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>46239</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>46282</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46239</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>46283</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45562</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46283</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45258</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46241</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>46286</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>46283</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>45400</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46241</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>46241</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>44610</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>44887</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>46245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>44953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46287</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>44951</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>46288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>44649</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>46132</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46288</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>46287</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>44502</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46287</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>45250</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59861,7 +59861,7 @@
         <v>44628</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45166</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60007,7 +60007,7 @@
         <v>46289</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>46248</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60163,7 +60163,7 @@
         <v>45259</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>46290</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>46290</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46289</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60470,7 +60470,7 @@
         <v>46289</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>46289</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>46248</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>46290</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>46290</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60855,7 +60855,7 @@
         <v>46290</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>46248</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45356</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>44566</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>44903</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45106</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>45258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45525</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45147</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61527,7 +61527,7 @@
         <v>45581</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>45678</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45470</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45726</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61829,7 +61829,7 @@
         <v>45196</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45106</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>45324</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>44465</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>44949</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62194,7 +62194,7 @@
         <v>44830</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45036</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45112</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62418,7 +62418,7 @@
         <v>44903</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>44904</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>45057</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45510</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>44876</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62798,7 +62798,7 @@
         <v>45673</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>45419</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63022,7 +63022,7 @@
         <v>45149</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63095,7 +63095,7 @@
         <v>45244</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63168,7 +63168,7 @@
         <v>45147</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63241,7 +63241,7 @@
         <v>45699</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>45328</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>45386</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>45590</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>45629</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45518</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>44869</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45510</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45244</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45645</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>45532</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>45575</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64122,7 +64122,7 @@
         <v>45107</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64195,7 +64195,7 @@
         <v>45093</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45624</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64346,7 +64346,7 @@
         <v>45684</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45684</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64492,7 +64492,7 @@
         <v>45433</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>45335</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>45323</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>45534</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64789,7 +64789,7 @@
         <v>45562</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>45562</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64945,7 +64945,7 @@
         <v>45562</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
         <v>45777</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45587</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65164,7 +65164,7 @@
         <v>45460</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45169</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>45783</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>45786</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>44683</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45790</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65607,7 +65607,7 @@
         <v>45790</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65685,7 +65685,7 @@
         <v>45789</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45791</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65836,7 +65836,7 @@
         <v>45792</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65914,7 +65914,7 @@
         <v>45792</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>45545</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>44127</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>44671</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>44606</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66299,7 +66299,7 @@
         <v>44606</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>44578</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>44606</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44606</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>44606</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66689,7 +66689,7 @@
         <v>44606</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66767,7 +66767,7 @@
         <v>44606</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45266</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66923,7 +66923,7 @@
         <v>45266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67001,7 +67001,7 @@
         <v>45266</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67079,7 +67079,7 @@
         <v>44834</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45266</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>44901</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67313,7 +67313,7 @@
         <v>45266</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>44901</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45266</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45266</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         <v>45356</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67698,7 +67698,7 @@
         <v>45247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67776,7 +67776,7 @@
         <v>44901</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67854,7 +67854,7 @@
         <v>45316</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45680</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45247</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>45266</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>45266</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68317,7 +68317,7 @@
         <v>45247</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68395,7 +68395,7 @@
         <v>45247</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68473,7 +68473,7 @@
         <v>44901</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68551,7 +68551,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68629,7 +68629,7 @@
         <v>45247</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68785,7 +68785,7 @@
         <v>44901</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68863,7 +68863,7 @@
         <v>45716</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>46037</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69019,7 +69019,7 @@
         <v>46036</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>46013</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69175,7 +69175,7 @@
         <v>45691</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45993</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44532</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45384</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44889</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45799</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>45155</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46064</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>46133</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45028</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45845</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>45842</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46171</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45772</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46203</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44762</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>46265</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>46268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46227</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46261</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45062</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45786</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45335</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46013</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44465</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44515</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44510</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45713</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45621</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45681</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45268</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45414</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45414</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45373</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45338</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45400</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44770</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45401</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45441</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45434</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45425</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45244</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45398</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45562</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45443</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44812</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45420</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45366</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44834</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45226</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45371</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45533</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45258</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44984</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45435</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45435</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>46020</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46018</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46018</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>46020</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45140</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45793</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45404</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>46030</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45793</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45754</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44903</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45797</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46030</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44540</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45799</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45799</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45895</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45739</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45898</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45148</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46048</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45902</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45475</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45902</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>46050</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>46049</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46050</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46050</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46050</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45050</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45905</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45905</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45905</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46052</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45909</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46057</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44938</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45212</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45562</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45562</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45562</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45918</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45492</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45922</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45922</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45922</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45103</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45842</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>46072</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45033</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>44883</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45420</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45201</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45201</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45201</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45926</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45927</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>45930</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45379</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45927</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45928</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45932</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45546</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45807</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45608</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45754</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45933</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>46087</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45446</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45933</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45933</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45282</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45037</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45933</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45933</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46091</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45938</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46090</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45390</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>46094</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45941</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>46098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45946</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46099</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46098</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46101</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>46101</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45811</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46104</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45765</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45713</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45947</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45811</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>46105</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>46104</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45951</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>46106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46106</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>46106</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45562</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>46106</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45954</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>46106</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>46111</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>46108</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45954</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45812</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>46108</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45811</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45671</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45960</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45623</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45960</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46122</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>46122</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45132</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>46122</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46126</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45812</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45967</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45006</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45051</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45461</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45211</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>46127</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>46128</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45975</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>46129</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>46129</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45980</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45436</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45980</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>46133</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>46134</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>46133</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46133</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46134</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45758</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>46133</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45988</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45615</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45819</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>44757</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44694</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45152</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44770</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45818</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45838</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45684</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45996</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44896</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45097</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45999</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45201</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45833</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44817</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45057</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45783</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>46136</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45786</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46003</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>46003</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46003</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45450</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46006</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46003</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45720</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46006</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>46007</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>46008</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46020</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45223</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45638</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45484</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45819</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46010</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>46010</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>46139</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45328</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45791</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45873</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44937</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45821</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46140</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46140</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45796</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45155</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46140</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44809</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45469</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45469</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44851</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45826</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45826</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45525</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45733</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45846</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44790</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>46141</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46141</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44915</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44526</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46141</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>46141</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45461</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45769</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45826</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>46058</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45264</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44537</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46142</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>46142</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45054</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44571</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45758</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46146</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44924</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45831</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45261</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45741</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>44896</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44817</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45090</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44839</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>46150</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>46150</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46149</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>46150</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45351</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44883</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46155</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46155</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45772</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>46155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45429</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45103</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>46160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46160</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45447</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45562</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45684</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46161</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45841</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45190</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45841</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46029</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>44950</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>44950</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>46162</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>46163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>46164</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45845</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45845</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45502</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46164</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45784</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45770</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45947</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45869</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45565</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45831</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44901</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45831</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45854</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45854</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45079</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46168</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46168</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45793</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>46171</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45519</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>46171</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45489</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>46171</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>46171</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46171</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45162</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46171</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46171</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45084</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>44951</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>46174</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45838</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46177</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46177</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44938</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45343</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46176</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>46177</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45475</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45475</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45428</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45335</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45035</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44567</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46181</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44622</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46178</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45720</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46181</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>46182</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46182</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46182</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>46182</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45107</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46185</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46185</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46185</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46185</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46184</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46184</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>46188</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>46188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>46189</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45547</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45145</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45526</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>46188</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45629</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>46191</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45824</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45874</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>46195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44824</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45608</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45582</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45572</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45638</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45356</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45569</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44603</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>44596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46198</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45211</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45750</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45559</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45618</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>46198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45069</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46198</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45644</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45506</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46200</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46200</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46203</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>46203</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45645</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44664</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>46203</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46203</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>46203</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45659</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45812</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46251</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>46206</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45055</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49317,7 +49317,7 @@
         <v>46209</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45763</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>46206</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>46252</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45232</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45121</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45716</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45226</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45385</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46206</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>44613</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>46205</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45679</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>46251</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>46209</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>46211</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45692</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44638</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46254</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45149</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>45703</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>46258</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45148</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>45107</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>44687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>46255</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>46213</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>46255</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>46254</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46254</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45244</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45684</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46260</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>46260</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45172</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45224</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46262</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46261</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45715</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45764</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46261</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45110</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>45645</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45279</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>46265</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45741</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>46265</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>46267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>46268</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>46225</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45250</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45723</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>45725</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>46272</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>46269</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>46269</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>46269</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
         <v>46268</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>44763</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>46272</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>46226</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45310</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46269</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46274</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>46274</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>46274</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>46267</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45211</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>45264</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>44595</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>46233</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>46275</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>44760</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>46275</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45618</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>46280</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55840,7 +55840,7 @@
         <v>45212</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>46280</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>46280</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>46280</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>44776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>46280</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>46279</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46233</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46280</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>46279</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56615,7 +56615,7 @@
         <v>46280</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45625</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45673</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46282</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>46282</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45476</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         <v>46239</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>46239</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>46282</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46281</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45534</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46282</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46282</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45509</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>46239</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>46282</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46239</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>46283</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45562</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46283</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45258</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46241</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>46286</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>46283</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>45400</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46241</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>46241</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>44610</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>44887</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>46245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>44953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46287</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>44951</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>46288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>44649</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>46132</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>46288</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>46287</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>44502</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>46287</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>45250</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59861,7 +59861,7 @@
         <v>44628</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45166</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60007,7 +60007,7 @@
         <v>46289</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>46248</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60163,7 +60163,7 @@
         <v>45259</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>46290</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>46290</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46289</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60470,7 +60470,7 @@
         <v>46289</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>46289</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>46248</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>46290</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>46290</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60855,7 +60855,7 @@
         <v>46290</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>46248</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45356</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>44566</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>44903</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45106</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>45258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45525</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45147</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61527,7 +61527,7 @@
         <v>45581</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>45678</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45470</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45726</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61829,7 +61829,7 @@
         <v>45196</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45106</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>45324</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>44465</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>44949</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62194,7 +62194,7 @@
         <v>44830</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45036</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45112</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62418,7 +62418,7 @@
         <v>44903</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>44904</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>45057</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45510</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>44876</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62798,7 +62798,7 @@
         <v>45673</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>45419</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>45308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63022,7 +63022,7 @@
         <v>45149</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63095,7 +63095,7 @@
         <v>45244</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63168,7 +63168,7 @@
         <v>45147</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63241,7 +63241,7 @@
         <v>45699</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>45328</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>45386</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>45590</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>45629</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45518</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>44869</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45510</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45244</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45645</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>45532</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>45575</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64122,7 +64122,7 @@
         <v>45107</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64195,7 +64195,7 @@
         <v>45093</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45624</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64346,7 +64346,7 @@
         <v>45684</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45684</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64492,7 +64492,7 @@
         <v>45433</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>45335</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>45323</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>45534</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64789,7 +64789,7 @@
         <v>45562</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>45562</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64945,7 +64945,7 @@
         <v>45562</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
         <v>45777</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45587</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65164,7 +65164,7 @@
         <v>45460</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45169</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>45783</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>45786</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>44683</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45790</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65607,7 +65607,7 @@
         <v>45790</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65685,7 +65685,7 @@
         <v>45789</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45791</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65836,7 +65836,7 @@
         <v>45792</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65914,7 +65914,7 @@
         <v>45792</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>45545</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>44127</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>44671</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>44606</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66299,7 +66299,7 @@
         <v>44606</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>44578</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>44606</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44606</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>44606</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66689,7 +66689,7 @@
         <v>44606</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66767,7 +66767,7 @@
         <v>44606</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45266</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66923,7 +66923,7 @@
         <v>45266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67001,7 +67001,7 @@
         <v>45266</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67079,7 +67079,7 @@
         <v>44834</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45266</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>44901</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67313,7 +67313,7 @@
         <v>45266</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>44901</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45266</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45266</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         <v>45356</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67698,7 +67698,7 @@
         <v>45247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67776,7 +67776,7 @@
         <v>44901</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67854,7 +67854,7 @@
         <v>45316</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45680</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45247</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>45266</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>45266</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68317,7 +68317,7 @@
         <v>45247</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68395,7 +68395,7 @@
         <v>45247</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68473,7 +68473,7 @@
         <v>44901</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68551,7 +68551,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68629,7 +68629,7 @@
         <v>45247</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68785,7 +68785,7 @@
         <v>44901</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68863,7 +68863,7 @@
         <v>45716</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>46037</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69019,7 +69019,7 @@
         <v>46036</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>46013</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69175,7 +69175,7 @@
         <v>45691</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46078</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>45637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45786</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45744</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45810</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45062</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44868</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45842</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45842</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45845</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45028</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>46171</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>46182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44762</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>46203</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46265</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46227</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>46268</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44889</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45384</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44510</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45321</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45335</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45103</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45489</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44839</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45678</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45152</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45335</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45786</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>46003</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>46003</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44664</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>46002</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>46002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>46007</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>46006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>46006</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>46006</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45414</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44901</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45419</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45328</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45545</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>46010</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45638</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45790</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46020</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>46020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46018</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>46018</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45343</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45891</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45715</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45937</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45653</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45729</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45898</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45898</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44834</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45051</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45623</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45902</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44887</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45435</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45659</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45905</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44649</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45905</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45905</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45792</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44903</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45250</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45909</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45793</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45793</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45754</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44770</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45575</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>46048</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46048</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45404</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45797</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45736</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>46049</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45799</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45799</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46050</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46050</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46050</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45918</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46050</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45807</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45754</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45546</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45055</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>46052</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45261</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45925</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>46057</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45461</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45385</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45547</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45927</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45927</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45443</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45475</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45811</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45933</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45608</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45932</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45933</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45933</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45933</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45562</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45562</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45562</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44566</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45938</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46072</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45941</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>46072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45250</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45224</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45947</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45147</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45946</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44817</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45811</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45946</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45433</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45812</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45954</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45954</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45954</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45954</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46087</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45673</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45961</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44790</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46091</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45106</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>46094</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44904</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46094</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46094</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46094</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45279</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46094</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45967</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>46098</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45971</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45968</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>46098</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>46098</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46099</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45975</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46101</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45975</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>46104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46101</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44628</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46106</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>46106</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45107</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>46106</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45033</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46106</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45201</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45201</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>46105</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45979</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45819</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46106</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45629</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>46108</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45980</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>45244</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46108</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45821</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>46111</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45821</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45581</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>46106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45103</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45988</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45625</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46122</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>46122</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44757</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45264</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45323</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45826</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45996</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45999</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45996</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>46129</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46127</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46129</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46128</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44687</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>46133</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>46133</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46133</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46133</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>46134</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45149</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45145</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>44812</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46134</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46133</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45166</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45510</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45401</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45425</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46139</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46020</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45645</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>44924</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45699</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45772</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45841</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45840</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45469</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45845</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45845</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45484</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>46136</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45786</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45791</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45770</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45266</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45684</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45565</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>44638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45784</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45838</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>44824</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45819</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45450</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45201</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45839</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44540</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45854</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45873</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45469</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45720</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45793</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45121</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45847</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45684</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45509</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44526</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45097</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45623</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>44937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45769</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45087</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46141</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45527</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>46140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>46141</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>44915</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>44938</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45833</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45838</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46141</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45371</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46141</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45684</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45713</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>46140</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44876</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>46141</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45084</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44502</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>46142</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>46142</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>46142</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>45562</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>46149</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45618</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>44613</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45645</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46150</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>46150</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45461</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>46150</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45351</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>45874</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46155</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>46155</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45152</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46155</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>46155</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45435</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45148</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>46160</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>46029</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44903</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46161</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46161</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>46160</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45502</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45057</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45758</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>46163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45429</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45569</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45947</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45356</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45869</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>46163</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44763</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45226</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45476</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46164</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45750</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45420</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>46164</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45831</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45831</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>46168</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46168</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45720</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45338</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>44984</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>46171</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45525</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>46174</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>46171</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>46171</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46171</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45812</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46171</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46171</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>45533</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>46171</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45287</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>46171</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>46176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>46177</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46178</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45614</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45226</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45765</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46177</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>46177</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46182</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45223</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45624</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46182</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46182</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45741</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45475</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45475</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45534</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45534</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44582</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45434</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>46184</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>46184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>46188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>46185</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45725</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45400</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>46188</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>46188</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>46188</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>46185</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45582</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>46185</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>46189</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>44567</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45526</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>46189</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45140</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46191</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44883</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45575</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46195</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45155</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44809</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45268</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45057</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46198</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46198</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46198</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45615</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46198</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>46200</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46200</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46191</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45470</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45562</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45079</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>46204</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46203</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>46203</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45441</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>46203</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>46206</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>46205</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45212</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>46206</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45203</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>46206</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45506</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46209</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>46209</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>44951</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45282</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>46211</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45684</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45436</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>44949</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46213</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>44760</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45050</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>46260</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>46261</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>46261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44817</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45681</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>46260</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45400</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>45373</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45525</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>46265</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46262</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52968,7 +52968,7 @@
         <v>45110</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>46269</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46269</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>44903</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46226</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>46225</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>44700</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>46225</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>45420</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45632</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45679</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>46272</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46268</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46269</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54493,7 +54493,7 @@
         <v>46269</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45398</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>46275</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46274</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>46274</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>46275</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54951,7 +54951,7 @@
         <v>46274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>46267</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>46275</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>46233</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46233</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46279</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>46279</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46280</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>46280</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>46280</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>46280</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>46280</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55960,7 +55960,7 @@
         <v>46280</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>45244</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>44596</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>46281</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>46283</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46282</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>46283</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>46239</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45054</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>46282</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>46239</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>46239</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>46283</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45212</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>46239</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>46282</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46282</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45645</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45244</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>46282</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>44610</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57734,7 +57734,7 @@
         <v>46286</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46287</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>46241</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>46132</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>46241</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>46287</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58202,7 +58202,7 @@
         <v>44950</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>44950</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>46241</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>45518</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>44830</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45428</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>46289</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>46288</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58801,7 +58801,7 @@
         <v>46288</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58879,7 +58879,7 @@
         <v>46288</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58957,7 +58957,7 @@
         <v>46289</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>46289</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>46289</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59186,7 +59186,7 @@
         <v>46245</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59259,7 +59259,7 @@
         <v>45371</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59332,7 +59332,7 @@
         <v>45763</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>46248</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>46290</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59644,7 +59644,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>46293</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46293</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>46290</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46293</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46293</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>46290</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46290</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45201</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46293</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60404,7 +60404,7 @@
         <v>46290</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60482,7 +60482,7 @@
         <v>46293</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>46293</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>46248</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45532</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>46293</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>46290</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>46248</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>46290</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>46290</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>46290</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45211</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>44896</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45559</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>46294</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61607,7 +61607,7 @@
         <v>45632</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>44694</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>46295</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61836,7 +61836,7 @@
         <v>46294</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>46251</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>46252</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62070,7 +62070,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>46295</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>46294</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>46294</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46294</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>45447</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45324</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>44571</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>45446</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45379</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>45713</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>46254</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>45758</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>45703</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>45414</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63283,7 +63283,7 @@
         <v>46255</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>46254</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>45684</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>46251</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63746,7 +63746,7 @@
         <v>45226</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45671</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63897,7 +63897,7 @@
         <v>45590</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63970,7 +63970,7 @@
         <v>44883</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64048,7 +64048,7 @@
         <v>45107</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64121,7 +64121,7 @@
         <v>45609</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45692</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45366</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64350,7 +64350,7 @@
         <v>44595</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64423,7 +64423,7 @@
         <v>45258</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64496,7 +64496,7 @@
         <v>45258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64574,7 +64574,7 @@
         <v>45328</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45029</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45175</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>45726</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>45244</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45673</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>45562</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65100,7 +65100,7 @@
         <v>45172</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>45201</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65246,7 +65246,7 @@
         <v>45492</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>45519</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65397,7 +65397,7 @@
         <v>44622</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
         <v>44851</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65543,7 +65543,7 @@
         <v>45510</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>45618</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65694,7 +65694,7 @@
         <v>44817</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         <v>45308</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65840,7 +65840,7 @@
         <v>45629</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65913,7 +65913,7 @@
         <v>45132</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65986,7 +65986,7 @@
         <v>45723</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66059,7 +66059,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66132,7 +66132,7 @@
         <v>45386</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45190</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66283,7 +66283,7 @@
         <v>45562</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45562</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66439,7 +66439,7 @@
         <v>45562</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66517,7 +66517,7 @@
         <v>45562</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66590,7 +66590,7 @@
         <v>44603</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66663,7 +66663,7 @@
         <v>45149</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66736,7 +66736,7 @@
         <v>45264</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66809,7 +66809,7 @@
         <v>45264</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66882,7 +66882,7 @@
         <v>45764</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>45035</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44770</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>45638</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67189,7 +67189,7 @@
         <v>45777</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67262,7 +67262,7 @@
         <v>45783</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67335,7 +67335,7 @@
         <v>45460</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>44683</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         <v>45587</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>45169</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>44127</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67705,7 +67705,7 @@
         <v>44671</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67783,7 +67783,7 @@
         <v>45266</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67861,7 +67861,7 @@
         <v>45266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67939,7 +67939,7 @@
         <v>44606</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68017,7 +68017,7 @@
         <v>45266</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>44834</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>44606</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45266</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>44578</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>44901</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68485,7 +68485,7 @@
         <v>45266</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68563,7 +68563,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68641,7 +68641,7 @@
         <v>45266</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68797,7 +68797,7 @@
         <v>44606</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>45356</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68948,7 +68948,7 @@
         <v>44606</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>45247</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>44901</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69182,7 +69182,7 @@
         <v>45316</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69255,7 +69255,7 @@
         <v>44901</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69333,7 +69333,7 @@
         <v>45680</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69411,7 +69411,7 @@
         <v>44606</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45247</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>45266</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69645,7 +69645,7 @@
         <v>44606</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69723,7 +69723,7 @@
         <v>44606</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69801,7 +69801,7 @@
         <v>45266</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         <v>45247</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69957,7 +69957,7 @@
         <v>45247</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70035,7 +70035,7 @@
         <v>44901</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70113,7 +70113,7 @@
         <v>44901</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45247</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70269,7 +70269,7 @@
         <v>45266</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>44901</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70425,7 +70425,7 @@
         <v>45716</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70503,7 +70503,7 @@
         <v>46037</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70581,7 +70581,7 @@
         <v>46036</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70659,7 +70659,7 @@
         <v>46013</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70737,7 +70737,7 @@
         <v>45691</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46078</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>45637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45786</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45744</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45810</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45062</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44868</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45842</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45842</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45772</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45845</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45028</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>46171</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>46182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44762</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>46203</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46265</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46227</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>46268</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44889</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>46240</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45384</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44510</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45321</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45335</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45103</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45489</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44839</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45678</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45152</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45335</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45786</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>46003</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>46003</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44664</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>46002</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>46002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>46007</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>46006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>46006</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>46006</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45414</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44901</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45419</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45328</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45545</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>46010</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45638</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45790</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46020</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>46020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46018</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>46018</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45343</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45891</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45715</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45937</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45653</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45729</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45898</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46030</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45898</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44834</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45051</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45623</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45902</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44887</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45435</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45659</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45905</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44649</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45905</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45905</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45792</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44903</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45250</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45909</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45793</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45824</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45793</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45754</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44770</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45575</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>46048</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46048</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45404</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45797</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45736</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>46049</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45799</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45799</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46050</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46050</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46050</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45918</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46050</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45807</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45754</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45922</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45546</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45055</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>46052</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45261</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45925</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>46057</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45461</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45385</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45547</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45927</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45927</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45443</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45475</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45811</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45933</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45608</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45932</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45933</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45933</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45933</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45562</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45562</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45562</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44566</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45938</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46072</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45941</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>46072</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45250</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45224</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45947</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45147</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45946</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44817</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45811</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45946</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45433</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45812</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45954</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45954</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45954</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45954</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46087</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45673</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45961</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44790</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46091</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45106</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>46094</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44904</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46094</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46094</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46094</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45279</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46094</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45967</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>46098</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45971</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45968</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>46098</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>46098</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>46099</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45975</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46101</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45975</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>46104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46101</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44628</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46106</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>46106</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45107</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>46106</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45033</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46106</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45201</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45201</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>46105</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45979</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45819</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46106</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45629</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>46108</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45980</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>45244</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46108</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45821</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>46111</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45821</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45581</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>46106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45103</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45988</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45625</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46122</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>46122</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44757</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45264</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45323</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45826</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45996</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45999</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45996</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>46129</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46127</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46129</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46128</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45831</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44687</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>46133</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>46133</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46133</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46133</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>46134</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45149</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45145</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>44812</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46134</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46133</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45166</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45510</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45401</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45425</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46139</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46020</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45645</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>44924</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45699</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45772</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45841</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45840</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45469</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45845</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45845</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45484</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>46136</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45786</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45791</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45770</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45266</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45684</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45565</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>44638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45784</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45838</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>44824</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45819</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45450</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45201</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45839</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44540</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45854</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45873</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45469</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45720</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45793</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45121</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45847</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45684</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45509</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>44526</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45097</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45623</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>44937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45769</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45087</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46141</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45527</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>46140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>46141</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>44915</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>44938</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45833</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45838</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46141</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45371</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46141</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45684</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45713</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>46140</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44876</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>46141</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45084</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44502</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>46142</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>46142</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>46142</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>45562</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>46149</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45618</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>44613</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45645</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46150</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>46150</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45461</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>46150</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45351</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>45874</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46155</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>46155</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45152</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46155</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>46155</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45435</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45148</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>46160</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>46029</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44903</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46161</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46161</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>46160</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45502</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45057</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45758</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>46163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45429</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45569</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45947</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45356</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45869</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>46163</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44763</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45226</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45476</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46164</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45750</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45420</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>46164</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45831</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45831</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>46168</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46168</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45720</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45338</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>44984</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>46171</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45525</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>46174</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>46171</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>46171</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46171</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45812</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46171</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46171</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>45533</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>46171</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45287</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>46171</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>46176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>46177</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46178</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45614</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45226</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45765</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46177</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>46177</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46182</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45223</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45624</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46182</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>46182</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45741</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45475</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45475</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45534</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45534</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44582</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45434</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>46184</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>46184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>46188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>46185</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45725</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45400</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>46188</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>46188</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>46188</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>46185</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45582</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>46185</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>46189</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>44567</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45526</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>46189</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45140</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>46191</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>44883</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45575</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46195</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45155</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44809</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45268</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45057</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46198</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46198</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46198</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45615</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46198</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>46200</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46200</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46191</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45470</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45562</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45079</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>46204</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46203</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>46203</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45441</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>46203</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>46206</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>46205</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45212</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>46206</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45203</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>46206</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45506</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46209</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>46209</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>44951</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45282</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>46211</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45684</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45436</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>44949</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46213</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>44760</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45050</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>46260</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>46261</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>46261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44817</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45681</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>46260</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45400</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>45373</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45525</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>46265</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46262</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52968,7 +52968,7 @@
         <v>45110</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>46269</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46269</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>44903</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46226</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>46225</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>44700</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>46225</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>45420</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45632</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45679</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>46272</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46268</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46269</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54493,7 +54493,7 @@
         <v>46269</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45398</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>46275</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46274</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>46274</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>46275</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54951,7 +54951,7 @@
         <v>46274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>46267</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>46275</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>46233</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46233</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46279</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>46279</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46280</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>46280</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>46280</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>46280</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>46280</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55960,7 +55960,7 @@
         <v>46280</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>45244</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>44596</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>46281</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>46283</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46282</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>46283</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>46239</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45054</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>46282</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56808,7 +56808,7 @@
         <v>46239</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>46239</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>46283</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45212</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>46239</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>46282</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46282</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45645</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45244</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>46282</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>44610</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57734,7 +57734,7 @@
         <v>46286</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46287</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>46241</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>46132</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>46241</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>46287</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58202,7 +58202,7 @@
         <v>44950</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>44950</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>46241</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>45518</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>44830</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45428</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>46289</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>46288</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58801,7 +58801,7 @@
         <v>46288</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58879,7 +58879,7 @@
         <v>46288</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58957,7 +58957,7 @@
         <v>46289</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>46289</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>46289</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59186,7 +59186,7 @@
         <v>46245</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59259,7 +59259,7 @@
         <v>45371</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59332,7 +59332,7 @@
         <v>45763</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>46248</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>46290</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59644,7 +59644,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>46293</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46293</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>46290</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46293</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46293</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>46290</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46290</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45201</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46293</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60404,7 +60404,7 @@
         <v>46290</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60482,7 +60482,7 @@
         <v>46293</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>46293</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>46248</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45532</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>46293</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>46290</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>46248</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>46290</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>46290</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>46290</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45211</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>44896</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45559</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>46294</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61607,7 +61607,7 @@
         <v>45632</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>44694</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>46295</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61836,7 +61836,7 @@
         <v>46294</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>46251</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>46252</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62070,7 +62070,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>46295</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>46294</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>46294</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46294</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>45447</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45324</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>44571</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>45446</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45379</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>45713</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>46254</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>45758</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>45703</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>45414</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63283,7 +63283,7 @@
         <v>46255</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>46254</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>45684</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>46251</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63746,7 +63746,7 @@
         <v>45226</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45671</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63897,7 +63897,7 @@
         <v>45590</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63970,7 +63970,7 @@
         <v>44883</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64048,7 +64048,7 @@
         <v>45107</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64121,7 +64121,7 @@
         <v>45609</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45692</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45366</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64350,7 +64350,7 @@
         <v>44595</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64423,7 +64423,7 @@
         <v>45258</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64496,7 +64496,7 @@
         <v>45258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64574,7 +64574,7 @@
         <v>45328</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45029</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64725,7 +64725,7 @@
         <v>45175</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>45726</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>45244</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45673</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>45562</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65100,7 +65100,7 @@
         <v>45172</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>45201</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65246,7 +65246,7 @@
         <v>45492</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>45519</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65397,7 +65397,7 @@
         <v>44622</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
         <v>44851</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65543,7 +65543,7 @@
         <v>45510</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>45618</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65694,7 +65694,7 @@
         <v>44817</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         <v>45308</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65840,7 +65840,7 @@
         <v>45629</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65913,7 +65913,7 @@
         <v>45132</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65986,7 +65986,7 @@
         <v>45723</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66059,7 +66059,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66132,7 +66132,7 @@
         <v>45386</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45190</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66283,7 +66283,7 @@
         <v>45562</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45562</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66439,7 +66439,7 @@
         <v>45562</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66517,7 +66517,7 @@
         <v>45562</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66590,7 +66590,7 @@
         <v>44603</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66663,7 +66663,7 @@
         <v>45149</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66736,7 +66736,7 @@
         <v>45264</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66809,7 +66809,7 @@
         <v>45264</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66882,7 +66882,7 @@
         <v>45764</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>45035</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44770</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>45638</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67189,7 +67189,7 @@
         <v>45777</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67262,7 +67262,7 @@
         <v>45783</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67335,7 +67335,7 @@
         <v>45460</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>44683</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         <v>45587</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>45169</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>44127</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67705,7 +67705,7 @@
         <v>44671</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67783,7 +67783,7 @@
         <v>45266</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67861,7 +67861,7 @@
         <v>45266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67939,7 +67939,7 @@
         <v>44606</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68017,7 +68017,7 @@
         <v>45266</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>44834</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>44606</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45266</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>44578</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>44901</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68485,7 +68485,7 @@
         <v>45266</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68563,7 +68563,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68641,7 +68641,7 @@
         <v>45266</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68797,7 +68797,7 @@
         <v>44606</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>45356</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68948,7 +68948,7 @@
         <v>44606</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>45247</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>44901</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69182,7 +69182,7 @@
         <v>45316</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69255,7 +69255,7 @@
         <v>44901</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69333,7 +69333,7 @@
         <v>45680</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69411,7 +69411,7 @@
         <v>44606</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45247</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69567,7 +69567,7 @@
         <v>45266</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69645,7 +69645,7 @@
         <v>44606</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69723,7 +69723,7 @@
         <v>44606</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69801,7 +69801,7 @@
         <v>45266</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         <v>45247</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69957,7 +69957,7 @@
         <v>45247</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70035,7 +70035,7 @@
         <v>44901</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70113,7 +70113,7 @@
         <v>44901</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45247</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70269,7 +70269,7 @@
         <v>45266</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>44901</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70425,7 +70425,7 @@
         <v>45716</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70503,7 +70503,7 @@
         <v>46037</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70581,7 +70581,7 @@
         <v>46036</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70659,7 +70659,7 @@
         <v>46013</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70737,7 +70737,7 @@
         <v>45691</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45246</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45441</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44566</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>46078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45384</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45062</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44889</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45545</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44603</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>45786</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45799</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>44762</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45943</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45842</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45971</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45842</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44868</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45028</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45743</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>46133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>46064</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46090</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46171</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>46203</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>46265</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46268</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46227</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46240</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46290</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46261</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44510</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44545</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44763</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44836</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44602</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44872</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44683</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44791</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44537</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44699</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>44545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44606</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44830</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44613</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45373</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45338</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44678</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44896</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45400</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45371</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45441</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45621</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45425</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45112</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44817</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44883</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44903</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45057</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45321</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45673</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45419</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45713</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45772</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45429</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45103</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45681</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45398</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45308</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45149</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45244</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45447</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45562</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45684</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45226</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45420</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45366</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>45527</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45699</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44834</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45401</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45414</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45328</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45287</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45226</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44901</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45812</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45386</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45079</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45371</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45590</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45258</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45152</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44984</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45435</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45435</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45518</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44869</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45510</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45519</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45799</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45489</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45244</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45084</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45895</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45729</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45739</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45898</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45898</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45532</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45575</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45645</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45093</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45624</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45902</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45684</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45684</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44540</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45433</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45335</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45343</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>44924</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45632</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45632</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45905</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45475</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45475</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45428</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45335</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45562</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45562</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45562</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44567</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45148</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45824</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45475</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44582</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45777</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45790</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45050</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45587</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45460</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45169</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45175</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45783</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45918</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44683</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45212</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45562</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45562</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45547</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45526</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45492</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45922</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45790</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45922</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45790</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45789</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45791</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45792</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44824</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45792</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45033</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>44883</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45925</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45608</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45926</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45582</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45420</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45201</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45201</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45201</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45572</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45927</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45638</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45930</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45927</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45615</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45623</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45379</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45928</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45404</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45559</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45618</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45793</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45644</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45797</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45932</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45754</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45446</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45506</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45933</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44664</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45799</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45933</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45799</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45659</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45390</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45933</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45933</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45938</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45842</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45763</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45546</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45938</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45807</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45232</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45608</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45754</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45716</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45765</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45226</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45385</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45713</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45810</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44613</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45937</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45679</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45939</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45811</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45811</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45811</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45812</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45562</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45812</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45941</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45811</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45946</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45692</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45812</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45812</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45211</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45149</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45703</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45671</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>44687</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45947</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45609</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45623</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45947</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45819</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45821</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45821</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45949</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45132</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45826</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45684</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45831</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45051</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45461</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45954</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45954</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45954</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45954</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45960</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45172</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45960</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45201</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45162</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>45961</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45764</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45436</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45966</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45110</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45968</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45967</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45841</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45615</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45971</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44757</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45645</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45841</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45845</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45845</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44694</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45784</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45152</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44770</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45854</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45854</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45975</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45793</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44896</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45201</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>44817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45653</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45057</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45250</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>45723</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45725</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45975</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45838</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44700</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45975</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45975</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>44763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45720</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45310</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>45980</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45223</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45979</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45824</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45211</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45087</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45264</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44595</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45356</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44937</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45569</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45750</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44760</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44809</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46094</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>46094</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46094</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45618</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>44851</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46098</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46098</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45525</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46099</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46101</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>44776</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46101</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>46104</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44790</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45461</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45625</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>46105</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45673</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>46104</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45476</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46106</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>46106</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45988</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45534</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46106</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46106</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46106</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45264</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45509</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>46108</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44537</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46108</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45054</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44571</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45562</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45758</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45258</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46106</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44924</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45741</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45400</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46122</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>46122</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45996</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45996</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>46122</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45999</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>46126</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>46127</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>44610</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>44887</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>46128</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46002</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46129</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44953</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>44951</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>46129</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>44649</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46002</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46133</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46003</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>46134</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>46133</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>46133</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46134</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>46006</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>46133</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>46003</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44502</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46003</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>46006</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>46133</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46006</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46003</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46006</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45250</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44628</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45166</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>46008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46007</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45819</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46008</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45638</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>46010</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46010</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>46010</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>45328</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45838</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46020</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>46018</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46018</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46020</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>46020</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45684</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45356</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45097</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45833</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>44566</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45937</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>44903</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45783</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>46136</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45786</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45525</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45147</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>45840</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45450</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46030</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>46034</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45581</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45847</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>46020</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45678</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45484</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45470</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46139</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45839</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45791</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45726</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45196</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45873</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45575</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>46140</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46140</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45106</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45796</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45324</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46140</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>46048</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46048</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45469</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45469</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45733</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45846</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>46049</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>46141</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46141</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44830</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44915</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>44526</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>46141</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45036</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>46141</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>46050</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46142</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46050</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>46141</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45769</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46058</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46052</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>46057</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46142</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>46142</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46141</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46146</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46150</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>46150</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46149</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>46150</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>46072</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>46072</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>46076</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45351</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>46155</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>46155</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>46155</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46155</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46087</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>46155</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>46155</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46160</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46160</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>46091</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>46160</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>46094</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53226,7 +53226,7 @@
         <v>46161</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53304,7 +53304,7 @@
         <v>46161</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         <v>46094</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>46029</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>46162</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46163</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>46164</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45502</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46164</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45947</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>45869</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45831</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45831</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>46168</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46168</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>46171</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>46171</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>46171</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54678,7 +54678,7 @@
         <v>46171</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54751,7 +54751,7 @@
         <v>46171</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>46171</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54897,7 +54897,7 @@
         <v>46171</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>46171</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>46174</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>46177</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>46177</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>46176</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>46177</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>46181</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>46178</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>46181</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>46182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         <v>46182</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>46182</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
         <v>46185</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>46185</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>46184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>46185</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46185</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46184</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>46184</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>46188</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>46188</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>46188</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>46189</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46188</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46191</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>46191</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46195</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>46198</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>46198</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>46198</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46198</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>46200</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46200</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>46203</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>46203</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>46203</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57909,7 +57909,7 @@
         <v>46203</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
         <v>46203</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>46191</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>46203</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>46204</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>46206</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>46209</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>46206</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>46205</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46209</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>46209</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>46213</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>46265</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>46265</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>46268</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>46267</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>46268</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>46225</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>46225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>46269</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>46272</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>46269</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59814,7 +59814,7 @@
         <v>46269</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>46268</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>46272</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>46272</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60126,7 +60126,7 @@
         <v>46226</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>46272</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60277,7 +60277,7 @@
         <v>46269</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>46274</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>46274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>46274</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         <v>46267</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>46233</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>46275</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>46275</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60896,7 +60896,7 @@
         <v>46275</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60969,7 +60969,7 @@
         <v>46280</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>46280</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61125,7 +61125,7 @@
         <v>46280</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>46280</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>46280</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>46279</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>46233</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>46280</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61593,7 +61593,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61671,7 +61671,7 @@
         <v>46280</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>46282</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61827,7 +61827,7 @@
         <v>46282</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>46239</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>46239</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62061,7 +62061,7 @@
         <v>46282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>46281</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>46282</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>46282</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46239</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62451,7 +62451,7 @@
         <v>46282</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46239</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46283</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>46283</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46241</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>46286</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>46283</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>46241</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>46241</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>46245</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>46287</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>46288</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>46132</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>46288</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63533,7 +63533,7 @@
         <v>46288</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>46287</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>46287</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>46289</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46290</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63923,7 +63923,7 @@
         <v>46290</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64001,7 +64001,7 @@
         <v>46289</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>46289</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>46289</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64230,7 +64230,7 @@
         <v>46290</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>46290</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>46290</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>46290</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>46290</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>46248</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64766,7 +64766,7 @@
         <v>46294</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>46294</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>46293</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64995,7 +64995,7 @@
         <v>46293</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65073,7 +65073,7 @@
         <v>46293</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>46294</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65229,7 +65229,7 @@
         <v>46290</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>46248</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65380,7 +65380,7 @@
         <v>46248</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>46293</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65536,7 +65536,7 @@
         <v>46293</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>46290</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46293</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65765,7 +65765,7 @@
         <v>46293</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>46290</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65994,7 +65994,7 @@
         <v>46294</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66072,7 +66072,7 @@
         <v>46290</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>46251</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>46295</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66301,7 +66301,7 @@
         <v>46295</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66379,7 +66379,7 @@
         <v>46252</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66457,7 +66457,7 @@
         <v>46295</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>46255</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66613,7 +66613,7 @@
         <v>46255</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>46254</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66769,7 +66769,7 @@
         <v>46300</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66842,7 +66842,7 @@
         <v>46254</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66920,7 +66920,7 @@
         <v>46300</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66993,7 +66993,7 @@
         <v>46300</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67066,7 +67066,7 @@
         <v>46254</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>46251</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>46255</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67300,7 +67300,7 @@
         <v>46290</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67373,7 +67373,7 @@
         <v>46301</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67446,7 +67446,7 @@
         <v>46258</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67524,7 +67524,7 @@
         <v>46261</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>46260</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67680,7 +67680,7 @@
         <v>46261</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67758,7 +67758,7 @@
         <v>46260</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67836,7 +67836,7 @@
         <v>46262</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67914,7 +67914,7 @@
         <v>46260</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67992,7 +67992,7 @@
         <v>44127</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>44671</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>44606</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>44606</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68304,7 +68304,7 @@
         <v>44578</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68382,7 +68382,7 @@
         <v>44606</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68460,7 +68460,7 @@
         <v>44606</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68538,7 +68538,7 @@
         <v>44606</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68616,7 +68616,7 @@
         <v>44606</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68694,7 +68694,7 @@
         <v>44606</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68772,7 +68772,7 @@
         <v>45266</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45266</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45266</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>44834</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>45266</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69162,7 +69162,7 @@
         <v>44901</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69240,7 +69240,7 @@
         <v>45266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69318,7 +69318,7 @@
         <v>44901</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45266</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45266</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>45356</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69625,7 +69625,7 @@
         <v>45247</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>44901</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69781,7 +69781,7 @@
         <v>45316</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>44901</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>45680</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70010,7 +70010,7 @@
         <v>45247</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70088,7 +70088,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70166,7 +70166,7 @@
         <v>45266</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70244,7 +70244,7 @@
         <v>45247</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45247</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>44901</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>44901</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70556,7 +70556,7 @@
         <v>45247</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70634,7 +70634,7 @@
         <v>45266</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>44901</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45716</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>46037</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>46036</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71024,7 +71024,7 @@
         <v>46013</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71102,7 +71102,7 @@
         <v>45691</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45246</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45441</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44566</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>46078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44606</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45384</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45062</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44889</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45545</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44603</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>45786</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45799</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>44762</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45188</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>45943</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45842</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45971</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45772</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45842</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44868</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45028</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45743</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>46133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>46064</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46090</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46171</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>46203</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>46265</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46268</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46227</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46240</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46290</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46261</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44510</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44545</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44763</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44836</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44602</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44872</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44683</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44791</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44537</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44699</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>44545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44606</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44830</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44613</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45373</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45338</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44678</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44896</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45400</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45371</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45441</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45621</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45425</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45112</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44817</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44883</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44903</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45057</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45321</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45673</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45419</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45713</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45772</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45429</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45103</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45681</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45398</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45308</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45149</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45244</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45447</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45147</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45562</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45684</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45226</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45420</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45366</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>45527</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45699</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44834</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45401</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45414</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45328</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45287</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45226</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44901</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45812</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45386</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45079</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45371</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45590</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45258</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45152</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44984</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45435</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45435</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45518</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44869</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45510</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45519</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45799</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45489</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45244</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45084</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45895</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45729</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45739</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45898</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45898</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45532</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45575</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45645</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45093</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45624</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45902</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45684</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45684</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44540</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45433</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45335</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45343</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>44924</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45632</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45632</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45905</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45475</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45475</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45428</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45335</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45562</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45562</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45562</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44567</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45148</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45824</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45475</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44582</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45777</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45790</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45050</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>45587</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45460</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45169</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45175</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45783</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45918</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44683</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45212</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45562</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45562</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45547</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45526</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45492</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45922</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45790</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45922</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45790</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45789</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45791</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45792</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44824</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45792</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45033</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>44883</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45925</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45608</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45926</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45582</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45420</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45201</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45201</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45201</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45572</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45927</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45638</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45930</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45927</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45615</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45623</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45379</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45928</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45404</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45559</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45618</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45793</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45644</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45797</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45932</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45754</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45446</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45506</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45933</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44664</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45799</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45933</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45799</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45659</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45390</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45933</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45933</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45938</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45842</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45763</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45546</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45938</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45807</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45232</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45608</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45754</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45716</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45765</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45226</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45385</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45713</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45810</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44613</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45937</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45679</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45939</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45811</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45811</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45811</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45812</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45562</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45812</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45941</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45811</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45946</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45692</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45812</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45812</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45211</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45149</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45703</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45671</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>44687</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45947</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45609</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45623</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45947</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45819</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45821</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45821</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45949</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45132</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45826</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45684</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45831</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45051</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45461</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45954</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45954</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45954</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45954</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45960</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45172</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45960</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45201</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45162</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>45961</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45764</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45436</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45966</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45110</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45968</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45967</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45841</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45615</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45971</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44757</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45645</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45841</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45845</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45845</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44694</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45784</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45152</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44770</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45854</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45854</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45975</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45793</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44896</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45201</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>44817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45653</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45057</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45250</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>45723</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45725</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45975</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45838</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44700</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45975</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45975</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>44763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45720</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45310</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>45980</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45223</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45979</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45824</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45211</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45087</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45264</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44595</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45356</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44937</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45569</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45750</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44760</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44809</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46094</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>46094</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46094</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45618</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>44851</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46098</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46098</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45525</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46099</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46101</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>44776</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46101</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>46104</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44790</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45461</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45625</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>46105</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45673</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>46104</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45476</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46106</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>46106</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45988</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45534</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46106</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46106</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46106</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45264</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45509</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>46108</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44537</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46108</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45054</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44571</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45562</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45758</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45258</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46106</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44924</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45741</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45400</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46122</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>46122</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45996</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45996</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>46122</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45999</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>46126</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>46127</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>44610</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>44887</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>46128</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46002</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46129</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44953</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>44951</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>46129</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>44649</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46002</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46133</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46003</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>46134</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>46133</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>46133</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46134</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>46006</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>46133</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>46003</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44502</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46003</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>46006</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>46133</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46006</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46003</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46006</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45250</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44628</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45166</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>46008</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46007</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45819</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46008</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45638</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>46010</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46010</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>46010</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>45328</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45838</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46020</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>46018</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46018</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46020</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>46020</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45684</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45356</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45097</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45833</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>44566</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45937</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>44903</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45783</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>46136</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45786</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45525</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45147</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>45840</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45450</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46030</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>46034</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45581</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45847</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>46020</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45678</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45484</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45470</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46139</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45839</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45791</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45726</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45196</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45873</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45575</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>46140</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46140</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45106</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45796</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45324</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46140</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>46048</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46048</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45469</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45469</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45733</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45846</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>46049</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>46141</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46141</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44830</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44915</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>44526</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>46141</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45036</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>46141</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>46050</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46142</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46050</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>46141</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45769</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46058</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46052</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>46057</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46142</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>46142</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46141</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46146</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46150</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>46150</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46149</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>46150</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>46072</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>46072</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>46076</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45351</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>46155</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>46155</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>46155</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46155</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46087</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>46155</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>46155</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46160</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46160</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>46091</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>46160</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>46094</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53226,7 +53226,7 @@
         <v>46161</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53304,7 +53304,7 @@
         <v>46161</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         <v>46094</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>46029</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>46162</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46163</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>46164</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45502</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46164</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45947</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>45869</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45831</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45831</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>46168</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46168</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>46171</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>46171</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>46171</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54678,7 +54678,7 @@
         <v>46171</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54751,7 +54751,7 @@
         <v>46171</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>46171</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54897,7 +54897,7 @@
         <v>46171</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>46171</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>46174</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>46177</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>46177</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>46176</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>46177</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>46181</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>46178</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>46181</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>46182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         <v>46182</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>46182</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
         <v>46185</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>46185</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>46184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>46185</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46185</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46184</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>46184</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>46188</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>46188</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>46188</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>46189</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46188</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46191</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>46191</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46195</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>46198</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>46198</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>46198</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46198</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>46200</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>46200</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>46203</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>46203</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>46203</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57909,7 +57909,7 @@
         <v>46203</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
         <v>46203</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>46191</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>46203</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>46204</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>46206</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>46209</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>46206</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>46205</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46209</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>46209</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>46213</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>46265</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>46265</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>46268</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>46267</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>46268</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>46225</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>46225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>46269</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>46272</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>46269</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59814,7 +59814,7 @@
         <v>46269</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>46268</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>46272</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>46272</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60126,7 +60126,7 @@
         <v>46226</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>46272</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60277,7 +60277,7 @@
         <v>46269</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>46274</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>46274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>46274</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         <v>46267</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>46233</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>46275</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>46275</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60896,7 +60896,7 @@
         <v>46275</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60969,7 +60969,7 @@
         <v>46280</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>46280</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61125,7 +61125,7 @@
         <v>46280</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>46280</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>46280</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>46279</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>46233</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>46280</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61593,7 +61593,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61671,7 +61671,7 @@
         <v>46280</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>46282</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61827,7 +61827,7 @@
         <v>46282</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>46239</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>46239</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62061,7 +62061,7 @@
         <v>46282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>46281</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>46282</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>46282</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46239</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62451,7 +62451,7 @@
         <v>46282</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46239</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46283</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>46283</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46241</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>46286</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>46283</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>46241</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>46241</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>46245</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>46287</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>46288</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>46132</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>46288</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63533,7 +63533,7 @@
         <v>46288</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>46287</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>46287</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>46289</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46290</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63923,7 +63923,7 @@
         <v>46290</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64001,7 +64001,7 @@
         <v>46289</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>46289</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>46289</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64230,7 +64230,7 @@
         <v>46290</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>46290</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>46290</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>46290</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>46290</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>46248</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64766,7 +64766,7 @@
         <v>46294</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>46294</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>46293</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64995,7 +64995,7 @@
         <v>46293</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65073,7 +65073,7 @@
         <v>46293</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>46294</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65229,7 +65229,7 @@
         <v>46290</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>46248</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65380,7 +65380,7 @@
         <v>46248</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>46293</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65536,7 +65536,7 @@
         <v>46293</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>46290</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46293</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65765,7 +65765,7 @@
         <v>46293</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>46290</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65994,7 +65994,7 @@
         <v>46294</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66072,7 +66072,7 @@
         <v>46290</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>46251</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>46295</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66301,7 +66301,7 @@
         <v>46295</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66379,7 +66379,7 @@
         <v>46252</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66457,7 +66457,7 @@
         <v>46295</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>46255</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66613,7 +66613,7 @@
         <v>46255</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>46254</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66769,7 +66769,7 @@
         <v>46300</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66842,7 +66842,7 @@
         <v>46254</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66920,7 +66920,7 @@
         <v>46300</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66993,7 +66993,7 @@
         <v>46300</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67066,7 +67066,7 @@
         <v>46254</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>46251</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>46255</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67300,7 +67300,7 @@
         <v>46290</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67373,7 +67373,7 @@
         <v>46301</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67446,7 +67446,7 @@
         <v>46258</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67524,7 +67524,7 @@
         <v>46261</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>46260</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67680,7 +67680,7 @@
         <v>46261</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67758,7 +67758,7 @@
         <v>46260</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67836,7 +67836,7 @@
         <v>46262</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67914,7 +67914,7 @@
         <v>46260</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67992,7 +67992,7 @@
         <v>44127</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>44671</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>44606</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>44606</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68304,7 +68304,7 @@
         <v>44578</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68382,7 +68382,7 @@
         <v>44606</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68460,7 +68460,7 @@
         <v>44606</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68538,7 +68538,7 @@
         <v>44606</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68616,7 +68616,7 @@
         <v>44606</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68694,7 +68694,7 @@
         <v>44606</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68772,7 +68772,7 @@
         <v>45266</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45266</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45266</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>44834</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>45266</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69162,7 +69162,7 @@
         <v>44901</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69240,7 +69240,7 @@
         <v>45266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69318,7 +69318,7 @@
         <v>44901</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45266</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45266</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>45356</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69625,7 +69625,7 @@
         <v>45247</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>44901</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69781,7 +69781,7 @@
         <v>45316</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>44901</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69932,7 +69932,7 @@
         <v>45680</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70010,7 +70010,7 @@
         <v>45247</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70088,7 +70088,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70166,7 +70166,7 @@
         <v>45266</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70244,7 +70244,7 @@
         <v>45247</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45247</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>44901</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>44901</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70556,7 +70556,7 @@
         <v>45247</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70634,7 +70634,7 @@
         <v>45266</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>44901</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45716</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>46037</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>46036</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71024,7 +71024,7 @@
         <v>46013</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71102,7 +71102,7 @@
         <v>45691</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45441</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44509</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45796</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45993</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>46078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46309</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>44606</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45247</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45155</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45845</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45028</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>46171</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44762</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46133</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45545</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44889</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46227</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>44603</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46240</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>46290</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45786</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>46265</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46261</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>46268</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45842</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45772</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44510</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44858</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45321</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45489</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45211</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45152</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45335</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45069</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45356</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45037</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45608</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45244</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45621</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45414</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45419</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45653</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45147</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45258</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44834</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45659</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44649</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45051</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45435</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45644</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44537</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45250</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44770</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44924</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45443</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45385</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45261</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45547</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45562</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45562</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45562</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44896</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45475</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45250</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45224</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44817</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45433</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45005</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45673</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44790</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45090</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44776</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45106</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44904</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45033</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45201</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45201</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45244</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45310</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45469</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45484</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>46136</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45786</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45103</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45625</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45819</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45450</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45783</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44757</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45264</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45323</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45799</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45839</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45889</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45873</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45891</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45469</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45895</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44687</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45148</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45739</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45729</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45846</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45898</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45149</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44526</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45898</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45898</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45097</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>46140</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>46141</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46141</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45902</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46140</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45833</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45510</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>46141</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45905</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45401</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45905</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45905</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45684</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45425</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45645</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45824</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>46141</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44924</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45699</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>46142</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45790</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46142</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45772</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45922</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45922</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45266</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45684</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44638</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>45925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44824</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45926</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45927</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45927</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>46150</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45933</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46150</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45932</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45933</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45933</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45933</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45933</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45201</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>46150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44540</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45937</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45351</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45720</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45941</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45121</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>46155</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45947</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45684</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45509</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45947</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45623</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44937</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45951</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45949</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45087</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45527</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46155</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45954</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45954</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45961</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45960</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46160</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45371</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45713</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46161</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46161</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>44876</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45966</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45967</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45971</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45084</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44502</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45971</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45968</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45006</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>46160</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45502</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46163</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45975</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45947</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45975</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45562</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45036</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45869</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45618</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>44613</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45979</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>46163</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45461</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45981</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45152</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46164</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46164</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45435</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44903</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46168</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46168</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45057</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45758</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45429</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45996</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45999</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45996</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44763</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45226</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45476</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45420</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46171</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>46003</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46003</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46002</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46002</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46003</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46003</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45720</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>46007</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46171</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46171</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45338</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>44984</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45525</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46171</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46008</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46008</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45328</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46010</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>46010</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46171</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46171</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46010</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45638</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45287</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45614</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45226</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45765</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46020</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46020</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46018</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46018</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46020</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46171</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46171</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45624</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45937</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45741</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45475</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45534</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45534</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44582</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45434</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45725</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45400</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46034</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46176</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46177</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46178</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45582</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46177</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46177</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44567</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45526</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45575</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46048</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46182</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46048</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46049</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46050</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45741</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>46050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46050</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>46181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46050</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>44883</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>46050</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46050</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46182</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45575</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46052</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>46182</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46182</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46057</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>44809</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45057</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46184</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45615</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>46184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>46184</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45470</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45562</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>46185</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>46188</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46188</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>46072</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>46072</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>46188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>46076</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45441</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>46185</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46185</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45107</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45212</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>45203</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45506</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>46090</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>46189</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>46087</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>44951</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>46091</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>46189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45282</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>46094</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46094</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45684</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>46191</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46094</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45436</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44949</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>46094</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>46098</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>46098</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>44760</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>46099</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45050</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46104</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46101</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46104</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46101</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46106</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46106</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>46106</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46105</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>44817</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45681</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46106</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>46106</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45400</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46108</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46108</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>46111</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46198</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46198</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45373</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>46106</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>46198</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45525</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46198</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46200</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>46200</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46191</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46122</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46122</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46122</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45110</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>44903</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>46126</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44700</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>46129</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>46127</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>46129</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46128</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45420</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45632</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46133</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>46133</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>46204</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46133</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46133</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46133</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46203</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45398</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>46134</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46203</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46203</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46203</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46139</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>46020</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46205</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45244</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>44596</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>46206</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45054</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>46209</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>46209</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45212</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>46209</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45645</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45244</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44610</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>46213</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>44950</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>44950</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>45518</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44830</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45428</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46226</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>46225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46272</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>46272</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45371</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45763</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46275</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46274</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45201</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45532</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46275</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44896</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45559</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>46233</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>46279</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46279</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45632</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>44694</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>46280</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46280</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46280</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45447</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45324</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44571</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>46282</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>46283</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51828,7 +51828,7 @@
         <v>45446</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45379</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>45713</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46283</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46239</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46239</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46239</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>46283</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45758</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>46239</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45703</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46282</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45414</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>46282</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>46282</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>45684</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46287</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>46286</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>46132</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46241</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45671</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>44883</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45107</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45609</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45692</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45366</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>44595</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46241</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45258</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45258</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>46289</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45328</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>46288</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>45029</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45175</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46288</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>46288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>46289</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>46289</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>46289</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>46245</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45726</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45244</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45673</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>46248</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45562</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>46290</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46290</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46290</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46293</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>45172</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46293</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>45201</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>46293</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45492</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>46293</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>46290</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45519</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>46290</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>44622</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>46293</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>46248</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46290</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46248</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>44851</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>45510</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>45618</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>46290</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>46290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>44817</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45308</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45629</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45132</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>45723</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46294</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>45572</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>45386</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46294</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46251</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>45190</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>46252</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>46295</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>46295</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59204,7 +59204,7 @@
         <v>46294</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45562</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59360,7 +59360,7 @@
         <v>45562</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45562</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45562</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>44603</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>46294</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46294</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45149</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>45264</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>45764</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>46254</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>46254</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>46254</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46251</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60427,7 +60427,7 @@
         <v>46255</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>45035</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46258</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>44770</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45638</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>45777</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>45783</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45460</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>44683</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45587</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>46255</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>46255</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>45169</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>46260</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45786</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>46301</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45791</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61922,7 +61922,7 @@
         <v>45790</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>46260</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62078,7 +62078,7 @@
         <v>45545</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>46290</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45790</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>46260</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>45623</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45792</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62541,7 +62541,7 @@
         <v>46307</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62619,7 +62619,7 @@
         <v>45792</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46307</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45793</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62843,7 +62843,7 @@
         <v>45793</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62916,7 +62916,7 @@
         <v>46307</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62994,7 +62994,7 @@
         <v>46262</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63072,7 +63072,7 @@
         <v>45615</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>46307</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>45754</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>46261</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>46261</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63457,7 +63457,7 @@
         <v>45404</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63535,7 +63535,7 @@
         <v>46307</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63613,7 +63613,7 @@
         <v>45797</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63686,7 +63686,7 @@
         <v>45797</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63759,7 +63759,7 @@
         <v>45797</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63832,7 +63832,7 @@
         <v>45736</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63905,7 +63905,7 @@
         <v>46307</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63983,7 +63983,7 @@
         <v>46307</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>45799</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>45799</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45799</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64285,7 +64285,7 @@
         <v>46308</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64363,7 +64363,7 @@
         <v>46265</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>46309</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>46265</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45842</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>46309</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>46309</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>45807</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>45754</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>45546</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65050,7 +65050,7 @@
         <v>45811</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65123,7 +65123,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>46309</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65274,7 +65274,7 @@
         <v>46309</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65352,7 +65352,7 @@
         <v>45810</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>45811</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65503,7 +65503,7 @@
         <v>45811</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65576,7 +65576,7 @@
         <v>46268</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65654,7 +65654,7 @@
         <v>46311</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>45812</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65810,7 +65810,7 @@
         <v>45812</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65888,7 +65888,7 @@
         <v>45812</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65966,7 +65966,7 @@
         <v>45811</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45812</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45812</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66195,7 +66195,7 @@
         <v>46269</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>46267</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>46269</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66429,7 +66429,7 @@
         <v>45211</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66502,7 +66502,7 @@
         <v>45819</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66580,7 +66580,7 @@
         <v>45818</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66658,7 +66658,7 @@
         <v>46267</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66731,7 +66731,7 @@
         <v>45821</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66809,7 +66809,7 @@
         <v>45821</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66882,7 +66882,7 @@
         <v>46269</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>46268</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>46269</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67272,7 +67272,7 @@
         <v>45826</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>45826</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67423,7 +67423,7 @@
         <v>45826</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67501,7 +67501,7 @@
         <v>45831</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>45841</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67657,7 +67657,7 @@
         <v>45841</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45841</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67813,7 +67813,7 @@
         <v>45845</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>45845</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45845</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>45770</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45565</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68178,7 +68178,7 @@
         <v>45784</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45854</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45854</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>45793</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45838</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45824</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68631,7 +68631,7 @@
         <v>45874</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45569</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68782,7 +68782,7 @@
         <v>45356</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68855,7 +68855,7 @@
         <v>45750</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45812</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>44127</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>44671</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69162,7 +69162,7 @@
         <v>45266</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69240,7 +69240,7 @@
         <v>45266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69318,7 +69318,7 @@
         <v>44606</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45266</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>44834</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>44606</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45266</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69708,7 +69708,7 @@
         <v>44578</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69786,7 +69786,7 @@
         <v>44901</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69864,7 +69864,7 @@
         <v>45266</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69942,7 +69942,7 @@
         <v>44901</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70020,7 +70020,7 @@
         <v>45266</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70098,7 +70098,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>44606</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70254,7 +70254,7 @@
         <v>45356</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70327,7 +70327,7 @@
         <v>44606</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70405,7 +70405,7 @@
         <v>45247</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70483,7 +70483,7 @@
         <v>44901</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70561,7 +70561,7 @@
         <v>45316</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70634,7 +70634,7 @@
         <v>44901</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>45680</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>44606</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>45247</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>45266</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71024,7 +71024,7 @@
         <v>44606</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71102,7 +71102,7 @@
         <v>44606</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71180,7 +71180,7 @@
         <v>45266</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71258,7 +71258,7 @@
         <v>45247</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71336,7 +71336,7 @@
         <v>45247</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71414,7 +71414,7 @@
         <v>44901</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71492,7 +71492,7 @@
         <v>44901</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71570,7 +71570,7 @@
         <v>45247</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>45266</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>44901</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>45716</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71882,7 +71882,7 @@
         <v>46037</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71960,7 +71960,7 @@
         <v>46036</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72038,7 +72038,7 @@
         <v>46013</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72116,7 +72116,7 @@
         <v>45691</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45036</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45441</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44509</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45796</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45993</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>46078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46309</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>44606</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45247</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45155</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45845</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45744</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45028</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>46171</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44762</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46133</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45545</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44889</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46227</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>44603</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46240</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>46290</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45786</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>46265</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46261</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>46268</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45842</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45772</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44510</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44566</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44858</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45321</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45489</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45211</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45152</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45335</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45069</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45356</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45037</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45608</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45244</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45621</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45414</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45419</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45653</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45147</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45258</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44834</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45659</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44649</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45051</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45435</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45644</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44537</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45250</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44770</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44924</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45443</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45385</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45261</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45547</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45562</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45562</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45562</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44896</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45475</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45250</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45224</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44817</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45433</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45005</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45673</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44790</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45090</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44776</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45106</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44904</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45033</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45201</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45201</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45244</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45310</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45469</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45484</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>46136</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45786</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45103</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45625</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45819</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45450</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45783</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>44757</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45264</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45323</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45799</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45839</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45889</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45873</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45891</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45469</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45895</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44687</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45148</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45739</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45729</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45846</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45898</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45149</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44526</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45898</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45898</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45097</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>46140</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>46141</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46141</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45902</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46140</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45833</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45510</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>46141</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45905</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45401</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45905</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45905</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45684</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45425</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45645</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45824</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>46141</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44924</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45699</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>46142</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45790</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46142</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45772</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45922</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45922</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45266</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45684</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44638</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>45925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44824</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45926</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45927</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45927</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>46150</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45933</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46150</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45932</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45933</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45933</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45933</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45933</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45201</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>46150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44540</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45937</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45351</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45720</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45941</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45121</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>46155</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45947</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45684</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45509</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45947</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45623</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44937</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45951</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45949</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45087</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45527</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46155</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45954</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45954</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45954</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45961</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45960</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46160</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45371</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45713</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46161</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46161</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>44876</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45966</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45967</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45971</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45084</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44502</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45971</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45968</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45006</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>46160</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45502</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46163</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45975</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45947</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45975</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45562</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45036</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45869</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45618</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>44613</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45979</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>46163</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45461</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45981</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45152</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46164</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46164</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45435</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44903</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46168</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46168</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45057</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45758</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45429</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45996</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45999</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45996</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44763</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45226</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45476</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45420</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46171</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>46003</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46003</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46002</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46002</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46003</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46003</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45720</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>46007</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46171</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>46006</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46171</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45338</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>44984</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45525</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46171</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46008</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46008</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45328</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46010</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>46010</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46171</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46171</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46010</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45638</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45287</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45614</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45226</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45765</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46020</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46020</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46018</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46018</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46020</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46171</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46171</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45624</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45937</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45741</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45475</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45534</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45534</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44582</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45434</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45725</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45400</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46034</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46176</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46177</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46178</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45582</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46177</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46177</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44567</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45526</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45575</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46048</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46182</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46048</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46049</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46050</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45741</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>46050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46050</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>46181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46050</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>44883</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>46050</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46050</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46182</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45575</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46052</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>46182</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46182</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46057</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>44809</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45057</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46184</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45615</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>46184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>46184</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45470</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45562</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>46185</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>46188</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46188</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>46072</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>46072</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>46188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>46076</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45441</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>46185</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46185</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45107</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45212</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>45203</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45506</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>46090</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>46189</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>46087</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>44951</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>46091</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>46189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45282</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>46094</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46094</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45684</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>46191</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46094</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45436</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44949</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>46094</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>46098</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>46098</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>44760</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>46099</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45050</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46104</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46101</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46104</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46101</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46106</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46106</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>46106</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46105</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>44817</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45681</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46106</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>46106</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45400</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46108</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46108</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>46111</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46198</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46198</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45373</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>46106</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>46198</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45525</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46198</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46200</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>46200</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46191</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46122</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46122</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46122</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45110</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>44903</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>46126</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44700</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>46129</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>46127</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>46129</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46128</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45420</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45632</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46133</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>46133</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>46204</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46133</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46133</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46133</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46203</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45398</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>46134</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46203</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46203</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46203</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46139</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>46020</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46205</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45244</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>44596</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>46206</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45054</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>46209</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>46209</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45212</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>46209</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45645</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45244</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44610</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>46213</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>44950</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>44950</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>45518</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44830</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45428</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46226</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>46225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46272</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>46272</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45371</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45763</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46275</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46274</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45201</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45532</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46275</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44896</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45559</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>46233</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>46279</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46279</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45632</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>44694</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>46280</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46280</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46280</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45447</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45324</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44571</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>46282</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>46283</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51828,7 +51828,7 @@
         <v>45446</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45379</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>45713</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46283</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46239</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46239</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46239</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>46283</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45758</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>46239</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45703</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46282</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45414</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>46282</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>46282</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>45684</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46287</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>46286</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>46132</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46241</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45671</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>44883</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45107</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45609</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45692</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45366</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>44595</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46241</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45258</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45258</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>46289</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45328</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>46288</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>45029</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45175</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46288</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>46288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>46289</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>46289</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>46289</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>46245</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45726</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45244</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45673</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>46248</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45562</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>46290</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46290</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46290</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46293</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>45172</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46293</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>45201</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>46293</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45492</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>46293</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>46290</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45519</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>46290</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>44622</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>46293</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>46248</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46290</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46248</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>44851</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>45510</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>45618</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>46290</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>46290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>44817</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45308</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45629</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>45132</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>45723</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46294</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>45572</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>45386</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46294</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>46251</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>45190</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>46252</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>46295</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>46295</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59204,7 +59204,7 @@
         <v>46294</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45562</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59360,7 +59360,7 @@
         <v>45562</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45562</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45562</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>44603</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>46294</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46294</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45149</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>45264</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>45764</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>46254</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>46254</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>46254</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46251</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60427,7 +60427,7 @@
         <v>46255</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>45035</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46258</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>44770</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>45638</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>45777</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>45783</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45460</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>44683</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45587</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>46255</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>46255</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>45169</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>46260</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45786</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>46301</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45791</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61922,7 +61922,7 @@
         <v>45790</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>46260</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62078,7 +62078,7 @@
         <v>45545</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>46290</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45790</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>46260</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>45623</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45792</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62541,7 +62541,7 @@
         <v>46307</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62619,7 +62619,7 @@
         <v>45792</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46307</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45793</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62843,7 +62843,7 @@
         <v>45793</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62916,7 +62916,7 @@
         <v>46307</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62994,7 +62994,7 @@
         <v>46262</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63072,7 +63072,7 @@
         <v>45615</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>46307</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>45754</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>46261</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>46261</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63457,7 +63457,7 @@
         <v>45404</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63535,7 +63535,7 @@
         <v>46307</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63613,7 +63613,7 @@
         <v>45797</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63686,7 +63686,7 @@
         <v>45797</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63759,7 +63759,7 @@
         <v>45797</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63832,7 +63832,7 @@
         <v>45736</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63905,7 +63905,7 @@
         <v>46307</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63983,7 +63983,7 @@
         <v>46307</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>45799</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>45799</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45799</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64285,7 +64285,7 @@
         <v>46308</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64363,7 +64363,7 @@
         <v>46265</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>46309</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>46265</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45842</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>46309</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>46309</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>45807</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>45754</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>45546</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65050,7 +65050,7 @@
         <v>45811</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65123,7 +65123,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>46309</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65274,7 +65274,7 @@
         <v>46309</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65352,7 +65352,7 @@
         <v>45810</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>45811</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65503,7 +65503,7 @@
         <v>45811</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65576,7 +65576,7 @@
         <v>46268</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65654,7 +65654,7 @@
         <v>46311</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>45812</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65810,7 +65810,7 @@
         <v>45812</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65888,7 +65888,7 @@
         <v>45812</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65966,7 +65966,7 @@
         <v>45811</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45812</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45812</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66195,7 +66195,7 @@
         <v>46269</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>46267</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>46269</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66429,7 +66429,7 @@
         <v>45211</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66502,7 +66502,7 @@
         <v>45819</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66580,7 +66580,7 @@
         <v>45818</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66658,7 +66658,7 @@
         <v>46267</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66731,7 +66731,7 @@
         <v>45821</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66809,7 +66809,7 @@
         <v>45821</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66882,7 +66882,7 @@
         <v>46269</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>46268</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>46269</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>46269</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67272,7 +67272,7 @@
         <v>45826</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>45826</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67423,7 +67423,7 @@
         <v>45826</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67501,7 +67501,7 @@
         <v>45831</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67579,7 +67579,7 @@
         <v>45841</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67657,7 +67657,7 @@
         <v>45841</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45841</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67813,7 +67813,7 @@
         <v>45845</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>45845</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45845</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>45770</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45565</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68178,7 +68178,7 @@
         <v>45784</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45854</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45854</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68407,7 +68407,7 @@
         <v>45793</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45838</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45824</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68631,7 +68631,7 @@
         <v>45874</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45569</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68782,7 +68782,7 @@
         <v>45356</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68855,7 +68855,7 @@
         <v>45750</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45812</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>44127</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>44671</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69162,7 +69162,7 @@
         <v>45266</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69240,7 +69240,7 @@
         <v>45266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69318,7 +69318,7 @@
         <v>44606</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45266</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>44834</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>44606</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45266</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69708,7 +69708,7 @@
         <v>44578</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69786,7 +69786,7 @@
         <v>44901</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69864,7 +69864,7 @@
         <v>45266</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69942,7 +69942,7 @@
         <v>44901</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70020,7 +70020,7 @@
         <v>45266</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70098,7 +70098,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>44606</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70254,7 +70254,7 @@
         <v>45356</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70327,7 +70327,7 @@
         <v>44606</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70405,7 +70405,7 @@
         <v>45247</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70483,7 +70483,7 @@
         <v>44901</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70561,7 +70561,7 @@
         <v>45316</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70634,7 +70634,7 @@
         <v>44901</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>45680</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>44606</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>45247</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>45266</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71024,7 +71024,7 @@
         <v>44606</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71102,7 +71102,7 @@
         <v>44606</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71180,7 +71180,7 @@
         <v>45266</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71258,7 +71258,7 @@
         <v>45247</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71336,7 +71336,7 @@
         <v>45247</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71414,7 +71414,7 @@
         <v>44901</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71492,7 +71492,7 @@
         <v>44901</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71570,7 +71570,7 @@
         <v>45247</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>45266</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>44901</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>45716</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71882,7 +71882,7 @@
         <v>46037</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71960,7 +71960,7 @@
         <v>46036</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72038,7 +72038,7 @@
         <v>46013</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72116,7 +72116,7 @@
         <v>45691</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46252</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45246</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45993</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46309</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45637</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>44606</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45247</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45744</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45943</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>45971</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>46203</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46227</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45786</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>46240</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45810</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46290</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>46090</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45842</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>46265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44582</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>46268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45845</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>46261</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>45028</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44762</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44868</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45743</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44502</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45250</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45166</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45244</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45321</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45713</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45681</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45268</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45891</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45729</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45898</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45739</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45898</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45898</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44770</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45401</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45902</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45414</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45414</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45373</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45338</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45203</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45400</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45356</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45905</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45905</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45905</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45909</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44566</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45824</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>46161</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45106</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>46029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45258</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>46162</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45147</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45502</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45869</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45831</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45678</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45470</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45831</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45196</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46168</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45926</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45371</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45927</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45927</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45441</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45434</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46171</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45324</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>46171</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45932</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46171</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46171</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45933</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45933</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45933</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45933</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45425</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44949</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45938</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44830</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>44817</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45938</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45036</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45941</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45244</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46177</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46176</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46177</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45946</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45398</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45562</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44812</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45443</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45226</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45420</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45366</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45527</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>46181</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44904</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45057</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45510</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45947</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44876</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45949</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45673</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45419</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46181</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45954</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>46182</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46182</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45954</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>46182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45308</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45149</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46185</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46184</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46185</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46184</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45960</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45960</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>46188</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45960</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>46188</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>46188</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45961</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46189</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46189</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>46191</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45966</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45699</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45966</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45226</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45968</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45328</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45967</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>46195</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45971</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45590</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45629</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45975</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>46198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45975</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45975</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46198</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>46198</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45518</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44869</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46200</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46200</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45371</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45510</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>46203</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>46191</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46203</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45244</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46204</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45533</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>46209</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45988</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45645</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45532</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>46206</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46209</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46209</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46211</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45093</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45624</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45684</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45684</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>46213</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45152</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44984</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45433</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45335</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45996</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45996</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45999</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45534</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45562</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45562</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45562</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46002</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45435</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45435</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>46002</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>46225</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46003</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46225</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46006</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46003</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46003</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46006</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45587</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46226</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45460</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>46006</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46003</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46008</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45783</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46007</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46233</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>46008</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>46280</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45638</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46280</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45786</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>46280</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45328</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44683</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46280</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46280</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46233</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46280</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46279</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>46280</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46020</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>46018</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46018</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46020</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>46020</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46282</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45790</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46239</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46282</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46281</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46282</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45790</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45937</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46282</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45791</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46239</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45792</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46283</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46283</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>45792</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46030</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46034</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46241</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45545</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45623</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>46283</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45140</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45793</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46241</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>46241</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45404</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45793</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46245</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45797</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>46287</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45754</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45575</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45797</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>46288</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45797</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>46048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46132</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46288</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46048</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46287</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46287</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45799</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45799</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45799</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>46050</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46050</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46050</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46289</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46050</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>46050</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46052</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46290</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>46290</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46289</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45546</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45807</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45608</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45754</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45810</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46290</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46290</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>46057</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>46294</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45811</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>46290</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45811</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45811</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45812</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46248</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46294</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45812</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45811</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39622,7 +39622,7 @@
         <v>46294</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>46293</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45812</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46293</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45812</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46293</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>46294</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>46290</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46248</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>46248</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45211</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46293</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46293</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46290</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>46293</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>46293</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45818</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>46290</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>46294</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>46290</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>46072</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>46072</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45819</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45821</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45821</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>46251</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>46076</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>46295</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>45826</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45826</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>46295</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>46252</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45826</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45831</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>46295</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>46087</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>46300</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46254</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46091</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46300</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46300</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>46254</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46094</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46094</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46094</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46094</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>46094</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>44903</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45841</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45841</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46098</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46098</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>46099</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>46098</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>46101</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>46255</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46101</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45841</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45845</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45845</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45845</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46104</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45784</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45770</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45565</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46105</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>46290</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>46106</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>46258</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>46106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>46106</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46106</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>46106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45645</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45854</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45854</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>46106</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46111</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>46108</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>46108</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45793</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>46106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45838</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46122</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46261</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>45824</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>46126</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46260</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46127</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45874</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46260</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46128</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>46307</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45569</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>46265</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46129</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45750</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>44924</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>46265</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45632</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45632</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>46262</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>46129</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>46307</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>46133</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>46133</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>46133</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45812</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46133</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46134</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46133</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45148</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>46133</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45475</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>44582</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45050</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46307</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>46307</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>46307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>46307</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45819</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>46307</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46308</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46309</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46309</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>46309</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46309</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>46267</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>44938</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45838</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>46267</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45212</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45562</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46309</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45562</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45562</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>45097</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>46268</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45492</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46311</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45833</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46268</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46311</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45783</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46136</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46269</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>46269</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>46269</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45786</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45840</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45450</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>46311</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>46269</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52383,7 +52383,7 @@
         <v>45103</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52456,7 +52456,7 @@
         <v>46269</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45847</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>46268</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>45614</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>46020</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45033</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45484</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44883</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45420</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>46139</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45201</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45201</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45201</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>45839</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>45791</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>45873</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>46140</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>46316</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>46140</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45796</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>46316</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>46316</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>46272</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46140</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54424,7 +54424,7 @@
         <v>46122</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54502,7 +54502,7 @@
         <v>46134</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45379</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45469</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45469</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54877,7 +54877,7 @@
         <v>46316</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54955,7 +54955,7 @@
         <v>45733</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>46275</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45846</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>46141</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>46141</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>44915</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>44526</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>46274</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>46141</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55647,7 +55647,7 @@
         <v>46141</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45446</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>46142</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46141</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45769</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>46058</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45282</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>46275</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>45037</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>46142</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46141</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46275</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>46274</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>46146</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>46274</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45390</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>46150</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>46150</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>46149</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>46150</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45765</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45713</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45351</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57396,7 +57396,7 @@
         <v>45562</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>46155</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>46155</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57630,7 +57630,7 @@
         <v>46155</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46155</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>46155</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>45005</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>46160</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45671</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45609</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>46160</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46160</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45623</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45132</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>45051</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>45461</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>45201</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45162</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45436</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45758</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45615</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>44757</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44694</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45152</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>44770</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>44896</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>45201</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45029</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>44817</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45653</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45057</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44700</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>45720</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45223</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>44937</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45155</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>44809</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>44851</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>45525</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>44790</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45461</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>45264</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45264</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>44537</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45054</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>44571</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>45758</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         <v>44924</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45261</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>45741</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>44896</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>44817</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45090</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>44839</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>45266</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>44883</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45772</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45429</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45103</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>45447</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>45562</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45190</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>44950</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>44950</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45287</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>44901</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45079</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45519</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45489</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45162</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>45084</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>44951</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>44938</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45343</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>45475</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45475</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
         <v>45428</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>45335</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45035</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63484,7 +63484,7 @@
         <v>44567</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>44622</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63630,7 +63630,7 @@
         <v>45720</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63703,7 +63703,7 @@
         <v>45175</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63776,7 +63776,7 @@
         <v>45107</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45547</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>45145</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45526</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64073,7 +64073,7 @@
         <v>45629</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>44824</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64224,7 +64224,7 @@
         <v>45608</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64302,7 +64302,7 @@
         <v>45582</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64380,7 +64380,7 @@
         <v>45572</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45638</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64526,7 +64526,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>44596</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64677,7 +64677,7 @@
         <v>45211</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64750,7 +64750,7 @@
         <v>45559</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64823,7 +64823,7 @@
         <v>45618</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64901,7 +64901,7 @@
         <v>45069</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64974,7 +64974,7 @@
         <v>45644</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>45506</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         <v>45645</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65198,7 +65198,7 @@
         <v>44664</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         <v>45659</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65344,7 +65344,7 @@
         <v>45055</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65417,7 +65417,7 @@
         <v>45763</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65495,7 +65495,7 @@
         <v>45232</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>45121</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65641,7 +65641,7 @@
         <v>45716</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65714,7 +65714,7 @@
         <v>45226</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45385</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65865,7 +65865,7 @@
         <v>44613</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65943,7 +65943,7 @@
         <v>45679</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         <v>45692</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44638</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>45149</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45703</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45148</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45107</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>44687</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>45244</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66610,7 +66610,7 @@
         <v>45684</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66683,7 +66683,7 @@
         <v>45172</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         <v>45224</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66829,7 +66829,7 @@
         <v>45715</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66902,7 +66902,7 @@
         <v>45764</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66980,7 +66980,7 @@
         <v>45110</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67053,7 +67053,7 @@
         <v>45645</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67131,7 +67131,7 @@
         <v>45279</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67204,7 +67204,7 @@
         <v>45741</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67282,7 +67282,7 @@
         <v>45250</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67355,7 +67355,7 @@
         <v>45723</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67428,7 +67428,7 @@
         <v>45725</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67501,7 +67501,7 @@
         <v>44763</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>45310</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67652,7 +67652,7 @@
         <v>45211</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>45087</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67871,7 +67871,7 @@
         <v>44595</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67944,7 +67944,7 @@
         <v>44760</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68017,7 +68017,7 @@
         <v>45618</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>45212</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>44776</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45625</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68324,7 +68324,7 @@
         <v>45673</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68397,7 +68397,7 @@
         <v>45476</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45534</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45509</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68631,7 +68631,7 @@
         <v>45562</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68709,7 +68709,7 @@
         <v>45258</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>45400</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68860,7 +68860,7 @@
         <v>44610</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>44887</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69016,7 +69016,7 @@
         <v>44953</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69089,7 +69089,7 @@
         <v>44951</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69167,7 +69167,7 @@
         <v>44649</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69245,7 +69245,7 @@
         <v>44127</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>44671</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>44606</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>44606</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>44578</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69635,7 +69635,7 @@
         <v>44606</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>44606</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         <v>44606</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69869,7 +69869,7 @@
         <v>44606</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69947,7 +69947,7 @@
         <v>44606</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70025,7 +70025,7 @@
         <v>45266</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70181,7 +70181,7 @@
         <v>45266</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70259,7 +70259,7 @@
         <v>44834</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70337,7 +70337,7 @@
         <v>45266</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70415,7 +70415,7 @@
         <v>44901</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>45266</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70571,7 +70571,7 @@
         <v>44901</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45266</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70727,7 +70727,7 @@
         <v>45266</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70805,7 +70805,7 @@
         <v>45356</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70878,7 +70878,7 @@
         <v>45247</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70956,7 +70956,7 @@
         <v>44901</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>45316</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>44901</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>45680</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71263,7 +71263,7 @@
         <v>45247</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71341,7 +71341,7 @@
         <v>45266</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>45266</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>45247</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45247</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71653,7 +71653,7 @@
         <v>44901</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71731,7 +71731,7 @@
         <v>44901</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71809,7 +71809,7 @@
         <v>45247</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
         <v>45266</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>44901</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72043,7 +72043,7 @@
         <v>45716</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72121,7 +72121,7 @@
         <v>46037</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72199,7 +72199,7 @@
         <v>46036</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72277,7 +72277,7 @@
         <v>46013</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72355,7 +72355,7 @@
         <v>45691</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46252</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45246</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45618</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>45678</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45036</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45441</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45993</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46309</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45637</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>44606</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45247</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44663</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45744</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45943</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45062</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>45971</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>46203</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46227</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45786</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>46240</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45810</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46290</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>46090</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45842</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>46265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44582</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>46268</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45845</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>46261</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>45028</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44762</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44868</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45743</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45335</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46013</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44526</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44538</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44613</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44836</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44537</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44502</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45250</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45166</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45244</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45321</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45713</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45681</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45268</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45891</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45729</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45898</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45739</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45898</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45898</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44770</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45401</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45902</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45414</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45414</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45373</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45338</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45203</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45400</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45356</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45905</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45905</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45905</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45909</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44566</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45824</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>46161</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45106</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>46029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45258</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>46162</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45147</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45502</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45869</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45831</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45678</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45470</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45831</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45196</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46168</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45926</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45371</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45927</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45927</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45441</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45434</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46171</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45324</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>46171</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45932</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46171</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46171</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45933</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45933</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45933</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45933</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45425</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44949</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45938</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44830</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>44817</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45938</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45036</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45939</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45941</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45244</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46177</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46176</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46177</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45946</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45398</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45562</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44812</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45443</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45226</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45420</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45366</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45527</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>46181</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44904</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45057</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45510</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45947</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44876</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45949</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45673</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45419</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46181</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45954</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>46182</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46182</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45954</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>46182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45308</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45149</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46185</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46184</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46185</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46184</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45960</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45960</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>46188</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45960</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>46188</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>46188</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45961</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46189</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46189</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>46191</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45966</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45699</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45966</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45226</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45968</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45328</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45967</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>46195</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45386</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45971</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45590</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45629</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45975</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>46198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45975</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45975</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46198</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>46198</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45518</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44869</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46200</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46200</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45371</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45510</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>46203</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>46191</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46203</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45244</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46204</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45533</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>46209</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45988</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45645</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45532</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>46206</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46209</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46209</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46211</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45093</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45624</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45684</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45684</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>46213</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45152</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44984</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45433</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45335</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45323</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45996</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45996</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45999</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45534</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45562</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45562</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45562</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46002</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45435</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45435</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>46002</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>46225</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>46003</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46225</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46006</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46003</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46003</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46006</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45587</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46226</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45460</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>46006</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46003</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46008</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45783</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46007</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46233</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>46008</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>46280</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45638</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46280</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45786</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>46280</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45328</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>44683</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46280</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46280</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46233</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46280</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46279</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>46280</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46020</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>46018</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46018</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46020</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>46020</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46282</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45790</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46239</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46282</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46281</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46282</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45790</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45937</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46282</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45791</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46239</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45792</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46283</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46283</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>45792</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46030</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>46034</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46241</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45545</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45623</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>46283</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45140</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45793</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46241</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>46241</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45404</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45793</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46245</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45797</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>46287</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45754</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45575</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45797</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>46288</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45797</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>46048</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46132</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46288</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46048</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46287</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46287</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45799</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45799</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45799</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>46050</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46050</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>46050</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46289</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46050</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>46050</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46052</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46290</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>46290</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46289</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45546</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45807</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45608</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45754</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45810</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46290</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46290</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>46057</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>46294</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45811</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>46290</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45811</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45811</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45812</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46248</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46294</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45812</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45811</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39622,7 +39622,7 @@
         <v>46294</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>46293</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45812</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46293</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45812</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46293</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>46294</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>46290</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46248</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>46248</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45211</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46293</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46293</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46290</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>46293</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>46293</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45818</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>46290</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>46294</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>46290</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>46072</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>46072</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45819</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45821</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45821</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>46251</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>46076</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>46295</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>45826</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45826</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>46295</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>46252</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45826</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45831</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>46295</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>46087</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>46300</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46254</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46091</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46300</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46300</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>46254</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46094</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46094</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46094</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46094</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>46094</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>44903</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45841</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45841</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46098</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46098</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>46099</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>46098</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>46101</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>46255</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46101</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45841</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45845</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45845</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45845</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46104</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45784</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45770</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45565</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46105</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>46290</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>46106</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>46258</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>46106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>46106</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46106</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>46106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45645</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45854</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45854</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>46106</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46111</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>46108</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>46108</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45793</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>46106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45838</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>44540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46122</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46261</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>45824</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>46126</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46260</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46127</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45874</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46260</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46128</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>46307</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45569</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>46265</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46129</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45750</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>44924</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>46265</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45632</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45632</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>46262</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>46129</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>46307</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>46133</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>46133</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>46133</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45812</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46133</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46134</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46133</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45148</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>46133</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45475</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>44582</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45050</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46307</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>46307</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>46307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>46307</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45819</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>46307</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46308</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46309</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46309</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>46309</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46309</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>46267</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>44938</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45838</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>46267</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45212</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45562</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46309</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45562</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45562</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>45097</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>46268</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45492</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46311</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45833</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46268</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46311</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45783</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46136</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46269</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>46269</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>46269</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45786</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45840</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45450</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>46311</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>46269</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52383,7 +52383,7 @@
         <v>45103</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52456,7 +52456,7 @@
         <v>46269</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45847</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>46268</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>45614</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>46020</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45033</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45484</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44883</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45420</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>46139</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45201</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45201</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45201</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>45839</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>45791</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>45873</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>46140</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>46316</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>46140</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45796</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>46316</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>46316</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>46272</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46140</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54424,7 +54424,7 @@
         <v>46122</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54502,7 +54502,7 @@
         <v>46134</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45379</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45469</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45469</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54877,7 +54877,7 @@
         <v>46316</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54955,7 +54955,7 @@
         <v>45733</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>46275</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45846</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>46141</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>46141</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>44915</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>44526</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>46274</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>46141</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55647,7 +55647,7 @@
         <v>46141</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45446</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>46142</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46141</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45769</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>46058</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45282</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>46275</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>45037</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>46142</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46141</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46275</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>46274</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>46146</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>46274</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45390</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>46150</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>46150</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>46149</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>46150</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45765</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45713</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45351</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57396,7 +57396,7 @@
         <v>45562</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>46155</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>46155</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57630,7 +57630,7 @@
         <v>46155</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46155</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>46155</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>45005</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>46160</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45671</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45609</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>46160</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46160</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45623</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45132</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>45051</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>45461</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>45201</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45162</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45436</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45758</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45615</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>44757</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44694</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45152</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>44770</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>44896</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>45201</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45029</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>44817</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45653</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45057</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44700</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>45720</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45223</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>44937</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45155</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>44809</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>44851</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>45525</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>44790</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45461</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>45264</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45264</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>44537</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45054</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>44571</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>45758</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         <v>44924</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45261</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>45741</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>44896</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>44817</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45090</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>44839</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>45266</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>44883</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45772</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45429</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45103</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>45447</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>45562</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45190</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>44950</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>44950</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45287</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>44901</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45079</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45519</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45489</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45162</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>45084</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>44951</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>44938</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45343</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>45475</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45475</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
         <v>45428</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>45335</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45035</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63484,7 +63484,7 @@
         <v>44567</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>44622</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63630,7 +63630,7 @@
         <v>45720</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63703,7 +63703,7 @@
         <v>45175</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63776,7 +63776,7 @@
         <v>45107</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45547</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>45145</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45526</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64073,7 +64073,7 @@
         <v>45629</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>44824</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64224,7 +64224,7 @@
         <v>45608</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64302,7 +64302,7 @@
         <v>45582</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64380,7 +64380,7 @@
         <v>45572</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45638</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64526,7 +64526,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>44596</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64677,7 +64677,7 @@
         <v>45211</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64750,7 +64750,7 @@
         <v>45559</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64823,7 +64823,7 @@
         <v>45618</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64901,7 +64901,7 @@
         <v>45069</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64974,7 +64974,7 @@
         <v>45644</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>45506</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         <v>45645</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65198,7 +65198,7 @@
         <v>44664</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         <v>45659</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65344,7 +65344,7 @@
         <v>45055</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65417,7 +65417,7 @@
         <v>45763</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65495,7 +65495,7 @@
         <v>45232</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>45121</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65641,7 +65641,7 @@
         <v>45716</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65714,7 +65714,7 @@
         <v>45226</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45385</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65865,7 +65865,7 @@
         <v>44613</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65943,7 +65943,7 @@
         <v>45679</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         <v>45692</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44638</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>45149</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45703</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45148</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45107</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>44687</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>45244</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66610,7 +66610,7 @@
         <v>45684</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66683,7 +66683,7 @@
         <v>45172</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         <v>45224</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66829,7 +66829,7 @@
         <v>45715</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66902,7 +66902,7 @@
         <v>45764</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66980,7 +66980,7 @@
         <v>45110</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67053,7 +67053,7 @@
         <v>45645</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67131,7 +67131,7 @@
         <v>45279</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67204,7 +67204,7 @@
         <v>45741</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67282,7 +67282,7 @@
         <v>45250</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67355,7 +67355,7 @@
         <v>45723</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67428,7 +67428,7 @@
         <v>45725</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67501,7 +67501,7 @@
         <v>44763</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67574,7 +67574,7 @@
         <v>45310</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67652,7 +67652,7 @@
         <v>45211</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>45087</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67871,7 +67871,7 @@
         <v>44595</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67944,7 +67944,7 @@
         <v>44760</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68017,7 +68017,7 @@
         <v>45618</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>45212</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>44776</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45625</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68324,7 +68324,7 @@
         <v>45673</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68397,7 +68397,7 @@
         <v>45476</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45534</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45509</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68631,7 +68631,7 @@
         <v>45562</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68709,7 +68709,7 @@
         <v>45258</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>45400</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68860,7 +68860,7 @@
         <v>44610</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>44887</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69016,7 +69016,7 @@
         <v>44953</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69089,7 +69089,7 @@
         <v>44951</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69167,7 +69167,7 @@
         <v>44649</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69245,7 +69245,7 @@
         <v>44127</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>44671</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>44606</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69479,7 +69479,7 @@
         <v>44606</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69557,7 +69557,7 @@
         <v>44578</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69635,7 +69635,7 @@
         <v>44606</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69713,7 +69713,7 @@
         <v>44606</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         <v>44606</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69869,7 +69869,7 @@
         <v>44606</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69947,7 +69947,7 @@
         <v>44606</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70025,7 +70025,7 @@
         <v>45266</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>45266</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70181,7 +70181,7 @@
         <v>45266</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70259,7 +70259,7 @@
         <v>44834</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70337,7 +70337,7 @@
         <v>45266</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70415,7 +70415,7 @@
         <v>44901</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>45266</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70571,7 +70571,7 @@
         <v>44901</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45266</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70727,7 +70727,7 @@
         <v>45266</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70805,7 +70805,7 @@
         <v>45356</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70878,7 +70878,7 @@
         <v>45247</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70956,7 +70956,7 @@
         <v>44901</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71034,7 +71034,7 @@
         <v>45316</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>44901</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>45680</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71263,7 +71263,7 @@
         <v>45247</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71341,7 +71341,7 @@
         <v>45266</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>45266</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>45247</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45247</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71653,7 +71653,7 @@
         <v>44901</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71731,7 +71731,7 @@
         <v>44901</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71809,7 +71809,7 @@
         <v>45247</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
         <v>45266</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>44901</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72043,7 +72043,7 @@
         <v>45716</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72121,7 +72121,7 @@
         <v>46037</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72199,7 +72199,7 @@
         <v>46036</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72277,7 +72277,7 @@
         <v>46013</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72355,7 +72355,7 @@
         <v>45691</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
